--- a/outputs/50916.xlsx
+++ b/outputs/50916.xlsx
@@ -222,43 +222,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -699,27 +699,27 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="str">
-        <f aca="false">IF(B12=B$2,C$2,IF(B12=B$3,C$3,IF(B12=B$4,C$4,IF(B12=B$5,C$5,IF(B12=B$6,C$6,IF(B12=B$7,C$7,IF(B12=B$8,C$8)))))))</f>
+        <f aca="false">IF(B$12=B$2,C$2,IF(B$12=B$3,C$3,IF(B$12=B$4,C$4,IF(B$12=B$5,C$5,IF(B$12=B$6,C$6,IF(B$12=B$7,C$7,IF(B$12=B$8,C$8)))))))</f>
         <v>Homeroom</v>
       </c>
       <c r="D12" s="4" t="str">
-        <f aca="false">IF(B12=B$2,D$2,IF(B12=B$3,D$3,IF(B12=B$4,D$4,IF(B12=B$5,D$5,IF(B12=B$6,D$6,IF(B12=B$7,D$7,IF(B12=B$8,D$8)))))))</f>
+        <f aca="false">IF(B$12=B$2,D$2,IF(B$12=B$3,D$3,IF(B$12=B$4,D$4,IF(B$12=B$5,D$5,IF(B$12=B$6,D$6,IF(B$12=B$7,D$7,IF(B$12=B$8,D$8)))))))</f>
         <v>French</v>
       </c>
       <c r="E12" s="4" t="str">
-        <f aca="false">IF(B12=B$2,E$2,IF(B12=B$3,E$3,IF(B12=B$4,E$4,IF(B12=B$5,E$5,IF(B12=B$6,E$6,IF(B12=B$7,E$7,IF(B12=B$8,E$8)))))))</f>
+        <f aca="false">IF(B$12=B$2,E$2,IF(B$12=B$3,E$3,IF(B$12=B$4,E$4,IF(B$12=B$5,E$5,IF(B$12=B$6,E$6,IF(B$12=B$7,E$7,IF(B$12=B$8,E$8)))))))</f>
         <v>Math</v>
       </c>
       <c r="F12" s="4" t="str">
-        <f aca="false">IF(B12=B$2,F$2,IF(B12=B$3,F$3,IF(B12=B$4,F$4,IF(B12=B$5,F$5,IF(B12=B$6,F$6,IF(B12=B$7,F$7,IF(B12=B$8,F$8)))))))</f>
+        <f aca="false">IF(B$12=B$2,F$2,IF(B$12=B$3,F$3,IF(B$12=B$4,F$4,IF(B$12=B$5,F$5,IF(B$12=B$6,F$6,IF(B$12=B$7,F$7,IF(B$12=B$8,F$8)))))))</f>
         <v>Science</v>
       </c>
       <c r="G12" s="4" t="str">
-        <f aca="false">IF(B12=B$2,G$2,IF(B12=B$3,G$3,IF(B12=B$4,G$4,IF(B12=B$5,G$5,IF(B12=B$6,G$6,IF(B12=B$7,G$7,IF(B12=B$8,G$8)))))))</f>
+        <f aca="false">IF(B$12=B$2,G$2,IF(B$12=B$3,G$3,IF(B$12=B$4,G$4,IF(B$12=B$5,G$5,IF(B$12=B$6,G$6,IF(B$12=B$7,G$7,IF(B$12=B$8,G$8)))))))</f>
         <v>Eng. Lang. Arts</v>
       </c>
       <c r="H12" s="4" t="str">
-        <f aca="false">IF(B12=B$2,H$2,IF(B12=B$3,H$3,IF(B12=B$4,H$4,IF(B12=B$5,H$5,IF(B12=B$6,H$6,IF(B12=B$7,H$7,IF(B12=B$8,H$8)))))))</f>
+        <f aca="false">IF(B$12=B$2,H$2,IF(B$12=B$3,H$3,IF(B$12=B$4,H$4,IF(B$12=B$5,H$5,IF(B$12=B$6,H$6,IF(B$12=B$7,H$7,IF(B$12=B$8,H$8)))))))</f>
         <v>Social Studies</v>
       </c>
     </row>
@@ -731,27 +731,27 @@
         <v>2</v>
       </c>
       <c r="C13" s="4" t="str">
-        <f aca="false">IF(B13=B$2,C$2,IF(B13=B$3,C$3,IF(B13=B$4,C$4,IF(B13=B$5,C$5,IF(B13=B$6,C$6,IF(B13=B$7,C$7,IF(B13=B$8,C$8)))))))</f>
+        <f aca="false">IF(B$13=B$2,C$2,IF(B$13=B$3,C$3,IF(B$13=B$4,C$4,IF(B$13=B$5,C$5,IF(B$13=B$6,C$6,IF(B$13=B$7,C$7,IF(B$13=B$8,C$8)))))))</f>
         <v>Homeroom</v>
       </c>
       <c r="D13" s="4" t="str">
-        <f aca="false">IF(B13=B$2,D$2,IF(B13=B$3,D$3,IF(B13=B$4,D$4,IF(B13=B$5,D$5,IF(B13=B$6,D$6,IF(B13=B$7,D$7,IF(B13=B$8,D$8)))))))</f>
+        <f aca="false">IF(B$13=B$2,D$2,IF(B$13=B$3,D$3,IF(B$13=B$4,D$4,IF(B$13=B$5,D$5,IF(B$13=B$6,D$6,IF(B$13=B$7,D$7,IF(B$13=B$8,D$8)))))))</f>
         <v>RE</v>
       </c>
       <c r="E13" s="4" t="str">
-        <f aca="false">IF(B13=B$2,E$2,IF(B13=B$3,E$3,IF(B13=B$4,E$4,IF(B13=B$5,E$5,IF(B13=B$6,E$6,IF(B13=B$7,E$7,IF(B13=B$8,E$8)))))))</f>
+        <f aca="false">IF(B$13=B$2,E$2,IF(B$13=B$3,E$3,IF(B$13=B$4,E$4,IF(B$13=B$5,E$5,IF(B$13=B$6,E$6,IF(B$13=B$7,E$7,IF(B$13=B$8,E$8)))))))</f>
         <v>Art</v>
       </c>
       <c r="F13" s="4" t="str">
-        <f aca="false">IF(B13=B$2,F$2,IF(B13=B$3,F$3,IF(B13=B$4,F$4,IF(B13=B$5,F$5,IF(B13=B$6,F$6,IF(B13=B$7,F$7,IF(B13=B$8,F$8)))))))</f>
+        <f aca="false">IF(B$13=B$2,F$2,IF(B$13=B$3,F$3,IF(B$13=B$4,F$4,IF(B$13=B$5,F$5,IF(B$13=B$6,F$6,IF(B$13=B$7,F$7,IF(B$13=B$8,F$8)))))))</f>
         <v>PE</v>
       </c>
       <c r="G13" s="4" t="str">
-        <f aca="false">IF(B13=B$2,G$2,IF(B13=B$3,G$3,IF(B13=B$4,G$4,IF(B13=B$5,G$5,IF(B13=B$6,G$6,IF(B13=B$7,G$7,IF(B13=B$8,G$8)))))))</f>
+        <f aca="false">IF(B$13=B$2,G$2,IF(B$13=B$3,G$3,IF(B$13=B$4,G$4,IF(B$13=B$5,G$5,IF(B$13=B$6,G$6,IF(B$13=B$7,G$7,IF(B$13=B$8,G$8)))))))</f>
         <v>Social Studies</v>
       </c>
       <c r="H13" s="4" t="str">
-        <f aca="false">IF(B13=B$2,H$2,IF(B13=B$3,H$3,IF(B13=B$4,H$4,IF(B13=B$5,H$5,IF(B13=B$6,H$6,IF(B13=B$7,H$7,IF(B13=B$8,H$8)))))))</f>
+        <f aca="false">IF(B$13=B$2,H$2,IF(B$13=B$3,H$3,IF(B$13=B$4,H$4,IF(B$13=B$5,H$5,IF(B$13=B$6,H$6,IF(B$13=B$7,H$7,IF(B$13=B$8,H$8)))))))</f>
         <v>Math</v>
       </c>
       <c r="L13" s="1"/>
@@ -764,27 +764,27 @@
         <v>3</v>
       </c>
       <c r="C14" s="4" t="str">
-        <f aca="false">IF(B14=B$2,C$2,IF(B14=B$3,C$3,IF(B14=B$4,C$4,IF(B14=B$5,C$5,IF(B14=B$6,C$6,IF(B14=B$7,C$7,IF(B14=B$8,C$8)))))))</f>
+        <f aca="false">IF(B$14=B$2,C$2,IF(B$14=B$3,C$3,IF(B$14=B$4,C$4,IF(B$14=B$5,C$5,IF(B$14=B$6,C$6,IF(B$14=B$7,C$7,IF(B$14=B$8,C$8)))))))</f>
         <v>Homeroom</v>
       </c>
       <c r="D14" s="4" t="str">
-        <f aca="false">IF(B14=B$2,D$2,IF(B14=B$3,D$3,IF(B14=B$4,D$4,IF(B14=B$5,D$5,IF(B14=B$6,D$6,IF(B14=B$7,D$7,IF(B14=B$8,D$8)))))))</f>
+        <f aca="false">IF(B$14=B$2,D$2,IF(B$14=B$3,D$3,IF(B$14=B$4,D$4,IF(B$14=B$5,D$5,IF(B$14=B$6,D$6,IF(B$14=B$7,D$7,IF(B$14=B$8,D$8)))))))</f>
         <v>French</v>
       </c>
       <c r="E14" s="4" t="str">
-        <f aca="false">IF(B14=B$2,E$2,IF(B14=B$3,E$3,IF(B14=B$4,E$4,IF(B14=B$5,E$5,IF(B14=B$6,E$6,IF(B14=B$7,E$7,IF(B14=B$8,E$8)))))))</f>
+        <f aca="false">IF(B$14=B$2,E$2,IF(B$14=B$3,E$3,IF(B$14=B$4,E$4,IF(B$14=B$5,E$5,IF(B$14=B$6,E$6,IF(B$14=B$7,E$7,IF(B$14=B$8,E$8)))))))</f>
         <v>Science</v>
       </c>
       <c r="F14" s="4" t="str">
-        <f aca="false">IF(B14=B$2,F$2,IF(B14=B$3,F$3,IF(B14=B$4,F$4,IF(B14=B$5,F$5,IF(B14=B$6,F$6,IF(B14=B$7,F$7,IF(B14=B$8,F$8)))))))</f>
+        <f aca="false">IF(B$14=B$2,F$2,IF(B$14=B$3,F$3,IF(B$14=B$4,F$4,IF(B$14=B$5,F$5,IF(B$14=B$6,F$6,IF(B$14=B$7,F$7,IF(B$14=B$8,F$8)))))))</f>
         <v>Math</v>
       </c>
       <c r="G14" s="4" t="str">
-        <f aca="false">IF(B14=B$2,G$2,IF(B14=B$3,G$3,IF(B14=B$4,G$4,IF(B14=B$5,G$5,IF(B14=B$6,G$6,IF(B14=B$7,G$7,IF(B14=B$8,G$8)))))))</f>
+        <f aca="false">IF(B$14=B$2,G$2,IF(B$14=B$3,G$3,IF(B$14=B$4,G$4,IF(B$14=B$5,G$5,IF(B$14=B$6,G$6,IF(B$14=B$7,G$7,IF(B$14=B$8,G$8)))))))</f>
         <v>RE</v>
       </c>
       <c r="H14" s="4" t="str">
-        <f aca="false">IF(B14=B$2,H$2,IF(B14=B$3,H$3,IF(B14=B$4,H$4,IF(B14=B$5,H$5,IF(B14=B$6,H$6,IF(B14=B$7,H$7,IF(B14=B$8,H$8)))))))</f>
+        <f aca="false">IF(B$14=B$2,H$2,IF(B$14=B$3,H$3,IF(B$14=B$4,H$4,IF(B$14=B$5,H$5,IF(B$14=B$6,H$6,IF(B$14=B$7,H$7,IF(B$14=B$8,H$8)))))))</f>
         <v>Eng. Lang. Arts</v>
       </c>
       <c r="L14" s="1"/>

--- a/outputs/50916.xlsx
+++ b/outputs/50916.xlsx
@@ -1,19 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="18350" windowHeight="6880"/>
   </bookViews>
   <sheets>
-    <sheet name="21-22 Schedule" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="21-22 Schedule" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -22,147 +29,279 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="28">
   <si>
-    <t xml:space="preserve">Day</t>
+    <t>Day</t>
   </si>
   <si>
-    <t xml:space="preserve">H1</t>
+    <t>H1</t>
   </si>
   <si>
-    <t xml:space="preserve">P1</t>
+    <t>P1</t>
   </si>
   <si>
-    <t xml:space="preserve">P2</t>
+    <t>P2</t>
   </si>
   <si>
-    <t xml:space="preserve">P3</t>
+    <t>P3</t>
   </si>
   <si>
-    <t xml:space="preserve">P4</t>
+    <t>P4</t>
   </si>
   <si>
-    <t xml:space="preserve">P5</t>
+    <t>P5</t>
   </si>
   <si>
-    <t xml:space="preserve">Homeroom</t>
+    <t>Homeroom</t>
   </si>
   <si>
-    <t xml:space="preserve">French</t>
+    <t>French</t>
   </si>
   <si>
-    <t xml:space="preserve">Math</t>
+    <t>Math</t>
   </si>
   <si>
-    <t xml:space="preserve">Science</t>
+    <t>Science</t>
   </si>
   <si>
-    <t xml:space="preserve">Eng. Lang. Arts</t>
+    <t>Eng. Lang. Arts</t>
   </si>
   <si>
-    <t xml:space="preserve">Social Studies</t>
+    <t>Social Studies</t>
   </si>
   <si>
-    <t xml:space="preserve">RE</t>
+    <t>RE</t>
   </si>
   <si>
-    <t xml:space="preserve">Art</t>
+    <t>Art</t>
   </si>
   <si>
-    <t xml:space="preserve">PE</t>
+    <t>PE</t>
   </si>
   <si>
-    <t xml:space="preserve">Home Economics</t>
+    <t>Home Economics</t>
   </si>
   <si>
-    <t xml:space="preserve">8-5(117)</t>
+    <t>8-5(117)</t>
   </si>
   <si>
-    <t xml:space="preserve">Weekend!</t>
+    <t>Weekend!</t>
   </si>
   <si>
-    <t xml:space="preserve">Thanksgiving</t>
+    <t>Thanksgiving</t>
   </si>
   <si>
-    <t xml:space="preserve">Remembrance Day</t>
+    <t>Remembrance Day</t>
   </si>
   <si>
-    <t xml:space="preserve">Christmas Break</t>
+    <t>Christmas Break</t>
   </si>
   <si>
-    <t xml:space="preserve">Term 2 Starts</t>
+    <t>Term 2 Starts</t>
   </si>
   <si>
-    <t xml:space="preserve">Holiday!</t>
+    <t>Holiday!</t>
   </si>
   <si>
-    <t xml:space="preserve">Easter Break</t>
+    <t>Easter Break</t>
   </si>
   <si>
-    <t xml:space="preserve">Victoria Day!</t>
+    <t>Victoria Day!</t>
   </si>
   <si>
-    <t xml:space="preserve">PD Day</t>
+    <t>PD Day</t>
   </si>
   <si>
-    <t xml:space="preserve">School's Out For Summer!</t>
+    <t>School's Out For Summer!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="ddd\ dd/mmm"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="ddd\ dd/mmm"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="0"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <u val="single"/>
+      <b/>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="0"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="等线"/>
-      <family val="0"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
-      <family val="0"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -172,130 +311,639 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="13">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <font>
         <b val="1"/>
+        <i val="0"/>
         <color rgb="FFFF0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -330,55 +978,119 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -386,24 +1098,33 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -416,7 +1137,13 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -426,13 +1153,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
+            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
+                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -440,6 +1169,7 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
+                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -447,37 +1177,36 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L301"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="5.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="2" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="3.71"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="46"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="2" width="9.14"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.14166666666667" style="2" customWidth="1"/>
+    <col min="3" max="8" width="11.7083333333333" style="2" customWidth="1"/>
+    <col min="9" max="9" width="3.70833333333333" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9.14166666666667" style="2"/>
+    <col min="11" max="11" width="25.7083333333333" style="2" customWidth="1"/>
+    <col min="12" max="12" width="46" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9.14166666666667" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="2:8">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -500,9 +1229,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="28" spans="1:8">
       <c r="A2" s="3"/>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -524,9 +1253,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:8">
       <c r="A3" s="3"/>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="4">
         <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -548,9 +1277,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="28" spans="1:8">
       <c r="A4" s="3"/>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="4">
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -572,9 +1301,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="28" spans="1:8">
       <c r="A5" s="3"/>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="4">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -596,9 +1325,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="28" spans="1:8">
       <c r="A6" s="3"/>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="4">
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -616,11 +1345,11 @@
       <c r="G6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" ht="28" spans="1:8">
       <c r="A7" s="3"/>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="4">
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -642,9 +1371,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="28" spans="1:8">
       <c r="A8" s="3"/>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="4">
         <v>7</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -666,164 +1395,154 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+    <row r="9" spans="1:8">
+      <c r="A9" s="7"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="7"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="10" t="s">
         <v>6</v>
       </c>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+    <row r="12" spans="1:8">
+      <c r="A12" s="3">
         <v>44447</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="4">
         <v>1</v>
       </c>
-      <c r="C12" s="4" t="str">
-        <f aca="false">IF(B$12=B$2,C$2,IF(B$12=B$3,C$3,IF(B$12=B$4,C$4,IF(B$12=B$5,C$5,IF(B$12=B$6,C$6,IF(B$12=B$7,C$7,IF(B$12=B$8,C$8)))))))</f>
-        <v>Homeroom</v>
+      <c r="C12" s="4" t="b">
+        <f>IF(A$12=A$2,C$2,IF(A$12=A$3,C$3,IF(A$12=A$4,C$4,IF(A$12=A$5,C$5,IF(A$12=A$6,C$6,IF(A$12=A$7,C$7,IF(A$12=A$8,C$8)))))))</f>
+        <v>0</v>
       </c>
       <c r="D12" s="4" t="str">
-        <f aca="false">IF(B$12=B$2,D$2,IF(B$12=B$3,D$3,IF(B$12=B$4,D$4,IF(B$12=B$5,D$5,IF(B$12=B$6,D$6,IF(B$12=B$7,D$7,IF(B$12=B$8,D$8)))))))</f>
+        <f>IF(B$12=B$2,D$2,IF(B$12=B$3,D$3,IF(B$12=B$4,D$4,IF(B$12=B$5,D$5,IF(B$12=B$6,D$6,IF(B$12=B$7,D$7,IF(B$12=B$8,D$8)))))))</f>
         <v>French</v>
       </c>
-      <c r="E12" s="4" t="str">
-        <f aca="false">IF(B$12=B$2,E$2,IF(B$12=B$3,E$3,IF(B$12=B$4,E$4,IF(B$12=B$5,E$5,IF(B$12=B$6,E$6,IF(B$12=B$7,E$7,IF(B$12=B$8,E$8)))))))</f>
-        <v>Math</v>
+      <c r="E12" s="4" t="b">
+        <f t="shared" ref="E12:H12" si="0">IF(C$12=C$2,E$2,IF(C$12=C$3,E$3,IF(C$12=C$4,E$4,IF(C$12=C$5,E$5,IF(C$12=C$6,E$6,IF(C$12=C$7,E$7,IF(C$12=C$8,E$8)))))))</f>
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="str">
-        <f aca="false">IF(B$12=B$2,F$2,IF(B$12=B$3,F$3,IF(B$12=B$4,F$4,IF(B$12=B$5,F$5,IF(B$12=B$6,F$6,IF(B$12=B$7,F$7,IF(B$12=B$8,F$8)))))))</f>
+        <f t="shared" si="0"/>
         <v>Science</v>
       </c>
-      <c r="G12" s="4" t="str">
-        <f aca="false">IF(B$12=B$2,G$2,IF(B$12=B$3,G$3,IF(B$12=B$4,G$4,IF(B$12=B$5,G$5,IF(B$12=B$6,G$6,IF(B$12=B$7,G$7,IF(B$12=B$8,G$8)))))))</f>
-        <v>Eng. Lang. Arts</v>
+      <c r="G12" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="H12" s="4" t="str">
-        <f aca="false">IF(B$12=B$2,H$2,IF(B$12=B$3,H$3,IF(B$12=B$4,H$4,IF(B$12=B$5,H$5,IF(B$12=B$6,H$6,IF(B$12=B$7,H$7,IF(B$12=B$8,H$8)))))))</f>
+        <f t="shared" si="0"/>
         <v>Social Studies</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+    <row r="13" spans="1:12">
+      <c r="A13" s="3">
         <v>44448</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="4">
         <v>2</v>
       </c>
-      <c r="C13" s="4" t="str">
-        <f aca="false">IF(B$13=B$2,C$2,IF(B$13=B$3,C$3,IF(B$13=B$4,C$4,IF(B$13=B$5,C$5,IF(B$13=B$6,C$6,IF(B$13=B$7,C$7,IF(B$13=B$8,C$8)))))))</f>
-        <v>Homeroom</v>
-      </c>
+      <c r="C13" s="4"/>
       <c r="D13" s="4" t="str">
-        <f aca="false">IF(B$13=B$2,D$2,IF(B$13=B$3,D$3,IF(B$13=B$4,D$4,IF(B$13=B$5,D$5,IF(B$13=B$6,D$6,IF(B$13=B$7,D$7,IF(B$13=B$8,D$8)))))))</f>
-        <v>RE</v>
-      </c>
-      <c r="E13" s="4" t="str">
-        <f aca="false">IF(B$13=B$2,E$2,IF(B$13=B$3,E$3,IF(B$13=B$4,E$4,IF(B$13=B$5,E$5,IF(B$13=B$6,E$6,IF(B$13=B$7,E$7,IF(B$13=B$8,E$8)))))))</f>
-        <v>Art</v>
-      </c>
-      <c r="F13" s="4" t="str">
-        <f aca="false">IF(B$13=B$2,F$2,IF(B$13=B$3,F$3,IF(B$13=B$4,F$4,IF(B$13=B$5,F$5,IF(B$13=B$6,F$6,IF(B$13=B$7,F$7,IF(B$13=B$8,F$8)))))))</f>
-        <v>PE</v>
-      </c>
-      <c r="G13" s="4" t="str">
-        <f aca="false">IF(B$13=B$2,G$2,IF(B$13=B$3,G$3,IF(B$13=B$4,G$4,IF(B$13=B$5,G$5,IF(B$13=B$6,G$6,IF(B$13=B$7,G$7,IF(B$13=B$8,G$8)))))))</f>
-        <v>Social Studies</v>
-      </c>
-      <c r="H13" s="4" t="str">
-        <f aca="false">IF(B$13=B$2,H$2,IF(B$13=B$3,H$3,IF(B$13=B$4,H$4,IF(B$13=B$5,H$5,IF(B$13=B$6,H$6,IF(B$13=B$7,H$7,IF(B$13=B$8,H$8)))))))</f>
-        <v>Math</v>
-      </c>
+        <f t="shared" ref="D13:D14" si="1">IF(B$12=B$2,D$2,IF(B$12=B$3,D$3,IF(B$12=B$4,D$4,IF(B$12=B$5,D$5,IF(B$12=B$6,D$6,IF(B$12=B$7,D$7,IF(B$12=B$8,D$8)))))))</f>
+        <v>French</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+    <row r="14" spans="1:12">
+      <c r="A14" s="3">
         <v>44449</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="4">
         <v>3</v>
       </c>
-      <c r="C14" s="4" t="str">
-        <f aca="false">IF(B$14=B$2,C$2,IF(B$14=B$3,C$3,IF(B$14=B$4,C$4,IF(B$14=B$5,C$5,IF(B$14=B$6,C$6,IF(B$14=B$7,C$7,IF(B$14=B$8,C$8)))))))</f>
-        <v>Homeroom</v>
-      </c>
+      <c r="C14" s="4"/>
       <c r="D14" s="4" t="str">
-        <f aca="false">IF(B$14=B$2,D$2,IF(B$14=B$3,D$3,IF(B$14=B$4,D$4,IF(B$14=B$5,D$5,IF(B$14=B$6,D$6,IF(B$14=B$7,D$7,IF(B$14=B$8,D$8)))))))</f>
+        <f t="shared" si="1"/>
         <v>French</v>
       </c>
-      <c r="E14" s="4" t="str">
-        <f aca="false">IF(B$14=B$2,E$2,IF(B$14=B$3,E$3,IF(B$14=B$4,E$4,IF(B$14=B$5,E$5,IF(B$14=B$6,E$6,IF(B$14=B$7,E$7,IF(B$14=B$8,E$8)))))))</f>
-        <v>Science</v>
-      </c>
-      <c r="F14" s="4" t="str">
-        <f aca="false">IF(B$14=B$2,F$2,IF(B$14=B$3,F$3,IF(B$14=B$4,F$4,IF(B$14=B$5,F$5,IF(B$14=B$6,F$6,IF(B$14=B$7,F$7,IF(B$14=B$8,F$8)))))))</f>
-        <v>Math</v>
-      </c>
-      <c r="G14" s="4" t="str">
-        <f aca="false">IF(B$14=B$2,G$2,IF(B$14=B$3,G$3,IF(B$14=B$4,G$4,IF(B$14=B$5,G$5,IF(B$14=B$6,G$6,IF(B$14=B$7,G$7,IF(B$14=B$8,G$8)))))))</f>
-        <v>RE</v>
-      </c>
-      <c r="H14" s="4" t="str">
-        <f aca="false">IF(B$14=B$2,H$2,IF(B$14=B$3,H$3,IF(B$14=B$4,H$4,IF(B$14=B$5,H$5,IF(B$14=B$6,H$6,IF(B$14=B$7,H$7,IF(B$14=B$8,H$8)))))))</f>
-        <v>Eng. Lang. Arts</v>
-      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+    <row r="15" spans="1:12">
+      <c r="A15" s="3">
         <v>44450</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="B15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+    <row r="16" spans="1:12">
+      <c r="A16" s="3">
         <v>44451</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
+      <c r="B16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
+    <row r="17" spans="1:12">
+      <c r="A17" s="3">
         <v>44452</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="4">
         <v>4</v>
       </c>
       <c r="C17" s="4"/>
@@ -834,25 +1553,25 @@
       <c r="H17" s="4"/>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
+    <row r="18" spans="1:8">
+      <c r="A18" s="3">
         <v>44453</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="4">
         <v>5</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="3">
         <v>44454</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="4">
         <v>6</v>
       </c>
       <c r="C19" s="4"/>
@@ -862,11 +1581,11 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
+    <row r="20" spans="1:8">
+      <c r="A20" s="3">
         <v>44455</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="4">
         <v>7</v>
       </c>
       <c r="C20" s="4"/>
@@ -876,11 +1595,11 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="n">
+    <row r="21" spans="1:8">
+      <c r="A21" s="3">
         <v>44456</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="4">
         <v>1</v>
       </c>
       <c r="C21" s="4"/>
@@ -890,39 +1609,39 @@
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="n">
+    <row r="22" spans="1:8">
+      <c r="A22" s="3">
         <v>44457</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="n">
+      <c r="B22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="3">
         <v>44458</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="n">
+      <c r="B23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="3">
         <v>44459</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="4">
         <v>2</v>
       </c>
       <c r="C24" s="4"/>
@@ -932,11 +1651,11 @@
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="n">
+    <row r="25" spans="1:8">
+      <c r="A25" s="3">
         <v>44460</v>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="4">
         <v>3</v>
       </c>
       <c r="C25" s="4"/>
@@ -946,11 +1665,11 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="n">
+    <row r="26" spans="1:8">
+      <c r="A26" s="3">
         <v>44461</v>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="4">
         <v>4</v>
       </c>
       <c r="C26" s="4"/>
@@ -960,25 +1679,25 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="n">
+    <row r="27" spans="1:8">
+      <c r="A27" s="3">
         <v>44462</v>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" s="4">
         <v>5</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-    </row>
-    <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="n">
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="3">
         <v>44463</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="4">
         <v>6</v>
       </c>
       <c r="C28" s="4"/>
@@ -988,39 +1707,39 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="n">
+    <row r="29" spans="1:8">
+      <c r="A29" s="3">
         <v>44464</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-    </row>
-    <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="n">
+      <c r="B29" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="3">
         <v>44465</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="n">
+      <c r="B30" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="3">
         <v>44466</v>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="4">
         <v>7</v>
       </c>
       <c r="C31" s="4"/>
@@ -1030,11 +1749,11 @@
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="n">
+    <row r="32" spans="1:8">
+      <c r="A32" s="3">
         <v>44467</v>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="4">
         <v>1</v>
       </c>
       <c r="C32" s="4"/>
@@ -1044,11 +1763,11 @@
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="n">
+    <row r="33" spans="1:8">
+      <c r="A33" s="3">
         <v>44468</v>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="4">
         <v>2</v>
       </c>
       <c r="C33" s="4"/>
@@ -1058,11 +1777,11 @@
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="n">
+    <row r="34" spans="1:8">
+      <c r="A34" s="3">
         <v>44469</v>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="4">
         <v>3</v>
       </c>
       <c r="C34" s="4"/>
@@ -1072,11 +1791,11 @@
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="n">
+    <row r="35" spans="1:8">
+      <c r="A35" s="3">
         <v>44470</v>
       </c>
-      <c r="B35" s="4" t="n">
+      <c r="B35" s="4">
         <v>4</v>
       </c>
       <c r="C35" s="4"/>
@@ -1086,53 +1805,53 @@
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="n">
+    <row r="36" spans="1:8">
+      <c r="A36" s="3">
         <v>44471</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-    </row>
-    <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="n">
+      <c r="B36" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="3">
         <v>44472</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-    </row>
-    <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="n">
+      <c r="B37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="3">
         <v>44473</v>
       </c>
-      <c r="B38" s="4" t="n">
+      <c r="B38" s="4">
         <v>5</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-    </row>
-    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="n">
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="3">
         <v>44474</v>
       </c>
-      <c r="B39" s="4" t="n">
+      <c r="B39" s="4">
         <v>6</v>
       </c>
       <c r="C39" s="4"/>
@@ -1142,11 +1861,11 @@
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="n">
+    <row r="40" spans="1:8">
+      <c r="A40" s="3">
         <v>44475</v>
       </c>
-      <c r="B40" s="4" t="n">
+      <c r="B40" s="4">
         <v>7</v>
       </c>
       <c r="C40" s="4"/>
@@ -1156,11 +1875,11 @@
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="n">
+    <row r="41" spans="1:8">
+      <c r="A41" s="3">
         <v>44476</v>
       </c>
-      <c r="B41" s="4" t="n">
+      <c r="B41" s="4">
         <v>1</v>
       </c>
       <c r="C41" s="4"/>
@@ -1170,11 +1889,11 @@
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
-    <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="n">
+    <row r="42" spans="1:8">
+      <c r="A42" s="3">
         <v>44477</v>
       </c>
-      <c r="B42" s="4" t="n">
+      <c r="B42" s="4">
         <v>2</v>
       </c>
       <c r="C42" s="4"/>
@@ -1184,53 +1903,53 @@
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
-    <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="n">
+    <row r="43" spans="1:8">
+      <c r="A43" s="3">
         <v>44478</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-    </row>
-    <row r="44" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="n">
+      <c r="B43" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="3">
         <v>44479</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-    </row>
-    <row r="45" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="n">
+      <c r="B44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="3">
         <v>44480</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="n">
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="3">
         <v>44481</v>
       </c>
-      <c r="B46" s="4" t="n">
+      <c r="B46" s="4">
         <v>3</v>
       </c>
       <c r="C46" s="4"/>
@@ -1240,11 +1959,11 @@
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
     </row>
-    <row r="47" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="n">
+    <row r="47" spans="1:8">
+      <c r="A47" s="3">
         <v>44482</v>
       </c>
-      <c r="B47" s="4" t="n">
+      <c r="B47" s="4">
         <v>4</v>
       </c>
       <c r="C47" s="4"/>
@@ -1254,11 +1973,11 @@
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="n">
+    <row r="48" spans="1:8">
+      <c r="A48" s="3">
         <v>44483</v>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B48" s="4">
         <v>5</v>
       </c>
       <c r="C48" s="4"/>
@@ -1268,11 +1987,11 @@
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="n">
+    <row r="49" spans="1:8">
+      <c r="A49" s="3">
         <v>44484</v>
       </c>
-      <c r="B49" s="4" t="n">
+      <c r="B49" s="4">
         <v>6</v>
       </c>
       <c r="C49" s="4"/>
@@ -1282,39 +2001,39 @@
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
-    <row r="50" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="n">
+    <row r="50" spans="1:8">
+      <c r="A50" s="3">
         <v>44485</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-    </row>
-    <row r="51" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="n">
+      <c r="B50" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="3">
         <v>44486</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-    </row>
-    <row r="52" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="n">
+      <c r="B51" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="3">
         <v>44487</v>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="B52" s="4">
         <v>7</v>
       </c>
       <c r="C52" s="4" t="s">
@@ -1326,11 +2045,11 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="n">
+    <row r="53" spans="1:8">
+      <c r="A53" s="3">
         <v>44488</v>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="B53" s="4">
         <v>1</v>
       </c>
       <c r="C53" s="4" t="s">
@@ -1342,11 +2061,11 @@
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
     </row>
-    <row r="54" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="n">
+    <row r="54" spans="1:8">
+      <c r="A54" s="3">
         <v>44489</v>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" s="4">
         <v>2</v>
       </c>
       <c r="C54" s="4" t="s">
@@ -1358,11 +2077,11 @@
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
     </row>
-    <row r="55" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="n">
+    <row r="55" spans="1:8">
+      <c r="A55" s="3">
         <v>44490</v>
       </c>
-      <c r="B55" s="4" t="n">
+      <c r="B55" s="4">
         <v>3</v>
       </c>
       <c r="C55" s="4" t="s">
@@ -1374,11 +2093,11 @@
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
     </row>
-    <row r="56" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="n">
+    <row r="56" spans="1:8">
+      <c r="A56" s="3">
         <v>44491</v>
       </c>
-      <c r="B56" s="4" t="n">
+      <c r="B56" s="4">
         <v>4</v>
       </c>
       <c r="C56" s="4" t="s">
@@ -1390,39 +2109,39 @@
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
     </row>
-    <row r="57" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="n">
+    <row r="57" spans="1:8">
+      <c r="A57" s="3">
         <v>44492</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-    </row>
-    <row r="58" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="3" t="n">
+      <c r="B57" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="3">
         <v>44493</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
-    </row>
-    <row r="59" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="3" t="n">
+      <c r="B58" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="3">
         <v>44494</v>
       </c>
-      <c r="B59" s="4" t="n">
+      <c r="B59" s="4">
         <v>5</v>
       </c>
       <c r="C59" s="4" t="s">
@@ -1434,11 +2153,11 @@
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
     </row>
-    <row r="60" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="n">
+    <row r="60" spans="1:8">
+      <c r="A60" s="3">
         <v>44495</v>
       </c>
-      <c r="B60" s="4" t="n">
+      <c r="B60" s="4">
         <v>6</v>
       </c>
       <c r="C60" s="4" t="s">
@@ -1450,11 +2169,11 @@
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
     </row>
-    <row r="61" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="3" t="n">
+    <row r="61" spans="1:8">
+      <c r="A61" s="3">
         <v>44496</v>
       </c>
-      <c r="B61" s="4" t="n">
+      <c r="B61" s="4">
         <v>7</v>
       </c>
       <c r="C61" s="4" t="s">
@@ -1466,11 +2185,11 @@
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
     </row>
-    <row r="62" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="3" t="n">
+    <row r="62" spans="1:8">
+      <c r="A62" s="3">
         <v>44497</v>
       </c>
-      <c r="B62" s="4" t="n">
+      <c r="B62" s="4">
         <v>1</v>
       </c>
       <c r="C62" s="4" t="s">
@@ -1482,11 +2201,11 @@
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
     </row>
-    <row r="63" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="3" t="n">
+    <row r="63" spans="1:8">
+      <c r="A63" s="3">
         <v>44498</v>
       </c>
-      <c r="B63" s="4" t="n">
+      <c r="B63" s="4">
         <v>2</v>
       </c>
       <c r="C63" s="4" t="s">
@@ -1498,39 +2217,39 @@
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
     </row>
-    <row r="64" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="n">
+    <row r="64" spans="1:8">
+      <c r="A64" s="3">
         <v>44499</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-    </row>
-    <row r="65" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="3" t="n">
+      <c r="B64" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="3">
         <v>44500</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-    </row>
-    <row r="66" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="3" t="n">
+      <c r="B65" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="3">
         <v>44501</v>
       </c>
-      <c r="B66" s="4" t="n">
+      <c r="B66" s="4">
         <v>3</v>
       </c>
       <c r="C66" s="4" t="s">
@@ -1542,11 +2261,11 @@
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
     </row>
-    <row r="67" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="3" t="n">
+    <row r="67" spans="1:8">
+      <c r="A67" s="3">
         <v>44502</v>
       </c>
-      <c r="B67" s="4" t="n">
+      <c r="B67" s="4">
         <v>4</v>
       </c>
       <c r="C67" s="4" t="s">
@@ -1558,11 +2277,11 @@
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
     </row>
-    <row r="68" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="3" t="n">
+    <row r="68" spans="1:8">
+      <c r="A68" s="3">
         <v>44503</v>
       </c>
-      <c r="B68" s="4" t="n">
+      <c r="B68" s="4">
         <v>5</v>
       </c>
       <c r="C68" s="4" t="s">
@@ -1574,11 +2293,11 @@
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
     </row>
-    <row r="69" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="3" t="n">
+    <row r="69" spans="1:8">
+      <c r="A69" s="3">
         <v>44504</v>
       </c>
-      <c r="B69" s="4" t="n">
+      <c r="B69" s="4">
         <v>6</v>
       </c>
       <c r="C69" s="4" t="s">
@@ -1590,11 +2309,11 @@
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
     </row>
-    <row r="70" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="n">
+    <row r="70" spans="1:8">
+      <c r="A70" s="3">
         <v>44505</v>
       </c>
-      <c r="B70" s="4" t="n">
+      <c r="B70" s="4">
         <v>7</v>
       </c>
       <c r="C70" s="4" t="s">
@@ -1606,39 +2325,39 @@
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
     </row>
-    <row r="71" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="3" t="n">
+    <row r="71" spans="1:8">
+      <c r="A71" s="3">
         <v>44506</v>
       </c>
-      <c r="B71" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-    </row>
-    <row r="72" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="3" t="n">
+      <c r="B71" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="3">
         <v>44507</v>
       </c>
-      <c r="B72" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-    </row>
-    <row r="73" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="n">
+      <c r="B72" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="3">
         <v>44508</v>
       </c>
-      <c r="B73" s="4" t="n">
+      <c r="B73" s="4">
         <v>1</v>
       </c>
       <c r="C73" s="4" t="s">
@@ -1650,11 +2369,11 @@
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
     </row>
-    <row r="74" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="3" t="n">
+    <row r="74" spans="1:8">
+      <c r="A74" s="3">
         <v>44509</v>
       </c>
-      <c r="B74" s="4" t="n">
+      <c r="B74" s="4">
         <v>2</v>
       </c>
       <c r="C74" s="4" t="s">
@@ -1666,14 +2385,14 @@
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
     </row>
-    <row r="75" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="3" t="n">
+    <row r="75" spans="1:8">
+      <c r="A75" s="3">
         <v>44510</v>
       </c>
-      <c r="B75" s="4" t="n">
+      <c r="B75" s="4">
         <v>3</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="C75" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D75" s="4"/>
@@ -1682,25 +2401,25 @@
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
     </row>
-    <row r="76" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="n">
+    <row r="76" spans="1:8">
+      <c r="A76" s="3">
         <v>44511</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-    </row>
-    <row r="77" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="3" t="n">
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="3">
         <v>44512</v>
       </c>
-      <c r="B77" s="4" t="n">
+      <c r="B77" s="4">
         <v>4</v>
       </c>
       <c r="C77" s="4" t="s">
@@ -1712,39 +2431,39 @@
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
     </row>
-    <row r="78" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="3" t="n">
+    <row r="78" spans="1:8">
+      <c r="A78" s="3">
         <v>44513</v>
       </c>
-      <c r="B78" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
-      <c r="H78" s="5"/>
-    </row>
-    <row r="79" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="n">
+      <c r="B78" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="3">
         <v>44514</v>
       </c>
-      <c r="B79" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
-    </row>
-    <row r="80" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3" t="n">
+      <c r="B79" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="3">
         <v>44515</v>
       </c>
-      <c r="B80" s="4" t="n">
+      <c r="B80" s="4">
         <v>5</v>
       </c>
       <c r="C80" s="4" t="s">
@@ -1756,11 +2475,11 @@
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
     </row>
-    <row r="81" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="3" t="n">
+    <row r="81" spans="1:8">
+      <c r="A81" s="3">
         <v>44516</v>
       </c>
-      <c r="B81" s="4" t="n">
+      <c r="B81" s="4">
         <v>6</v>
       </c>
       <c r="C81" s="4" t="s">
@@ -1772,11 +2491,11 @@
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
     </row>
-    <row r="82" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="3" t="n">
+    <row r="82" spans="1:8">
+      <c r="A82" s="3">
         <v>44517</v>
       </c>
-      <c r="B82" s="4" t="n">
+      <c r="B82" s="4">
         <v>7</v>
       </c>
       <c r="C82" s="4" t="s">
@@ -1788,11 +2507,11 @@
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
     </row>
-    <row r="83" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="3" t="n">
+    <row r="83" spans="1:8">
+      <c r="A83" s="3">
         <v>44518</v>
       </c>
-      <c r="B83" s="4" t="n">
+      <c r="B83" s="4">
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
@@ -1804,11 +2523,11 @@
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
     </row>
-    <row r="84" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="3" t="n">
+    <row r="84" spans="1:8">
+      <c r="A84" s="3">
         <v>44519</v>
       </c>
-      <c r="B84" s="4" t="n">
+      <c r="B84" s="4">
         <v>2</v>
       </c>
       <c r="C84" s="4" t="s">
@@ -1820,39 +2539,39 @@
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
     </row>
-    <row r="85" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="3" t="n">
+    <row r="85" spans="1:8">
+      <c r="A85" s="3">
         <v>44520</v>
       </c>
-      <c r="B85" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
-      <c r="G85" s="5"/>
-      <c r="H85" s="5"/>
-    </row>
-    <row r="86" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="3" t="n">
+      <c r="B85" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="3">
         <v>44521</v>
       </c>
-      <c r="B86" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C86" s="5"/>
-      <c r="D86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
-      <c r="G86" s="5"/>
-      <c r="H86" s="5"/>
-    </row>
-    <row r="87" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="3" t="n">
+      <c r="B86" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="3">
         <v>44522</v>
       </c>
-      <c r="B87" s="4" t="n">
+      <c r="B87" s="4">
         <v>3</v>
       </c>
       <c r="C87" s="4" t="s">
@@ -1864,11 +2583,11 @@
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
     </row>
-    <row r="88" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="3" t="n">
+    <row r="88" spans="1:8">
+      <c r="A88" s="3">
         <v>44523</v>
       </c>
-      <c r="B88" s="4" t="n">
+      <c r="B88" s="4">
         <v>4</v>
       </c>
       <c r="C88" s="4" t="s">
@@ -1880,11 +2599,11 @@
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
     </row>
-    <row r="89" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="3" t="n">
+    <row r="89" spans="1:8">
+      <c r="A89" s="3">
         <v>44524</v>
       </c>
-      <c r="B89" s="4" t="n">
+      <c r="B89" s="4">
         <v>5</v>
       </c>
       <c r="C89" s="4" t="s">
@@ -1896,11 +2615,11 @@
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
     </row>
-    <row r="90" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="3" t="n">
+    <row r="90" spans="1:8">
+      <c r="A90" s="3">
         <v>44525</v>
       </c>
-      <c r="B90" s="4" t="n">
+      <c r="B90" s="4">
         <v>6</v>
       </c>
       <c r="C90" s="4" t="s">
@@ -1912,11 +2631,11 @@
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
     </row>
-    <row r="91" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="3" t="n">
+    <row r="91" spans="1:8">
+      <c r="A91" s="3">
         <v>44526</v>
       </c>
-      <c r="B91" s="4" t="n">
+      <c r="B91" s="4">
         <v>7</v>
       </c>
       <c r="C91" s="4" t="s">
@@ -1928,39 +2647,39 @@
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
     </row>
-    <row r="92" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="3" t="n">
+    <row r="92" spans="1:8">
+      <c r="A92" s="3">
         <v>44527</v>
       </c>
-      <c r="B92" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C92" s="5"/>
-      <c r="D92" s="5"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
-      <c r="G92" s="5"/>
-      <c r="H92" s="5"/>
-    </row>
-    <row r="93" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="3" t="n">
+      <c r="B92" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="3">
         <v>44528</v>
       </c>
-      <c r="B93" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C93" s="5"/>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
-      <c r="H93" s="5"/>
-    </row>
-    <row r="94" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="3" t="n">
+      <c r="B93" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="3">
         <v>44529</v>
       </c>
-      <c r="B94" s="4" t="n">
+      <c r="B94" s="4">
         <v>1</v>
       </c>
       <c r="C94" s="4" t="s">
@@ -1972,11 +2691,11 @@
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
     </row>
-    <row r="95" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="3" t="n">
+    <row r="95" spans="1:8">
+      <c r="A95" s="3">
         <v>44530</v>
       </c>
-      <c r="B95" s="4" t="n">
+      <c r="B95" s="4">
         <v>2</v>
       </c>
       <c r="C95" s="4" t="s">
@@ -1988,11 +2707,11 @@
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
     </row>
-    <row r="96" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="3" t="n">
+    <row r="96" spans="1:8">
+      <c r="A96" s="3">
         <v>44531</v>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B96" s="4">
         <v>3</v>
       </c>
       <c r="C96" s="4" t="s">
@@ -2004,11 +2723,11 @@
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
     </row>
-    <row r="97" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="3" t="n">
+    <row r="97" spans="1:8">
+      <c r="A97" s="3">
         <v>44532</v>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B97" s="4">
         <v>4</v>
       </c>
       <c r="C97" s="4" t="s">
@@ -2020,11 +2739,11 @@
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
     </row>
-    <row r="98" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="3" t="n">
+    <row r="98" spans="1:10">
+      <c r="A98" s="3">
         <v>44533</v>
       </c>
-      <c r="B98" s="4" t="n">
+      <c r="B98" s="4">
         <v>5</v>
       </c>
       <c r="C98" s="4" t="s">
@@ -2035,41 +2754,41 @@
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
-      <c r="J98" s="10"/>
-    </row>
-    <row r="99" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="3" t="n">
+      <c r="J98" s="13"/>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="3">
         <v>44534</v>
       </c>
-      <c r="B99" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C99" s="5"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="5"/>
-    </row>
-    <row r="100" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="3" t="n">
+      <c r="B99" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="3">
         <v>44535</v>
       </c>
-      <c r="B100" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C100" s="5"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="5"/>
-    </row>
-    <row r="101" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="3" t="n">
+      <c r="B100" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="3">
         <v>44536</v>
       </c>
-      <c r="B101" s="4" t="n">
+      <c r="B101" s="4">
         <v>6</v>
       </c>
       <c r="C101" s="4" t="s">
@@ -2081,11 +2800,11 @@
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
     </row>
-    <row r="102" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="3" t="n">
+    <row r="102" spans="1:8">
+      <c r="A102" s="3">
         <v>44537</v>
       </c>
-      <c r="B102" s="4" t="n">
+      <c r="B102" s="4">
         <v>7</v>
       </c>
       <c r="C102" s="4" t="s">
@@ -2097,11 +2816,11 @@
       <c r="G102" s="4"/>
       <c r="H102" s="4"/>
     </row>
-    <row r="103" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="3" t="n">
+    <row r="103" spans="1:8">
+      <c r="A103" s="3">
         <v>44538</v>
       </c>
-      <c r="B103" s="4" t="n">
+      <c r="B103" s="4">
         <v>1</v>
       </c>
       <c r="C103" s="4" t="s">
@@ -2113,11 +2832,11 @@
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
     </row>
-    <row r="104" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="3" t="n">
+    <row r="104" spans="1:8">
+      <c r="A104" s="3">
         <v>44539</v>
       </c>
-      <c r="B104" s="4" t="n">
+      <c r="B104" s="4">
         <v>2</v>
       </c>
       <c r="C104" s="4" t="s">
@@ -2129,11 +2848,11 @@
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
     </row>
-    <row r="105" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="3" t="n">
+    <row r="105" spans="1:8">
+      <c r="A105" s="3">
         <v>44540</v>
       </c>
-      <c r="B105" s="4" t="n">
+      <c r="B105" s="4">
         <v>3</v>
       </c>
       <c r="C105" s="4" t="s">
@@ -2145,39 +2864,39 @@
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
     </row>
-    <row r="106" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="3" t="n">
+    <row r="106" spans="1:8">
+      <c r="A106" s="3">
         <v>44541</v>
       </c>
-      <c r="B106" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C106" s="5"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5"/>
-    </row>
-    <row r="107" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="3" t="n">
+      <c r="B106" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="4"/>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" s="3">
         <v>44542</v>
       </c>
-      <c r="B107" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C107" s="5"/>
-      <c r="D107" s="5"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="5"/>
-      <c r="G107" s="5"/>
-      <c r="H107" s="5"/>
-    </row>
-    <row r="108" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="3" t="n">
+      <c r="B107" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="3">
         <v>44543</v>
       </c>
-      <c r="B108" s="4" t="n">
+      <c r="B108" s="4">
         <v>4</v>
       </c>
       <c r="C108" s="4" t="s">
@@ -2189,11 +2908,11 @@
       <c r="G108" s="4"/>
       <c r="H108" s="4"/>
     </row>
-    <row r="109" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="3" t="n">
+    <row r="109" spans="1:8">
+      <c r="A109" s="3">
         <v>44544</v>
       </c>
-      <c r="B109" s="4" t="n">
+      <c r="B109" s="4">
         <v>5</v>
       </c>
       <c r="C109" s="4" t="s">
@@ -2205,11 +2924,11 @@
       <c r="G109" s="4"/>
       <c r="H109" s="4"/>
     </row>
-    <row r="110" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="3" t="n">
+    <row r="110" spans="1:8">
+      <c r="A110" s="3">
         <v>44545</v>
       </c>
-      <c r="B110" s="4" t="n">
+      <c r="B110" s="4">
         <v>6</v>
       </c>
       <c r="C110" s="4" t="s">
@@ -2221,11 +2940,11 @@
       <c r="G110" s="4"/>
       <c r="H110" s="4"/>
     </row>
-    <row r="111" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="3" t="n">
+    <row r="111" spans="1:8">
+      <c r="A111" s="3">
         <v>44546</v>
       </c>
-      <c r="B111" s="4" t="n">
+      <c r="B111" s="4">
         <v>7</v>
       </c>
       <c r="C111" s="4" t="s">
@@ -2237,11 +2956,11 @@
       <c r="G111" s="4"/>
       <c r="H111" s="4"/>
     </row>
-    <row r="112" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="3" t="n">
+    <row r="112" spans="1:8">
+      <c r="A112" s="3">
         <v>44547</v>
       </c>
-      <c r="B112" s="4" t="n">
+      <c r="B112" s="4">
         <v>1</v>
       </c>
       <c r="C112" s="4" t="s">
@@ -2253,39 +2972,39 @@
       <c r="G112" s="4"/>
       <c r="H112" s="4"/>
     </row>
-    <row r="113" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="3" t="n">
+    <row r="113" spans="1:8">
+      <c r="A113" s="3">
         <v>44548</v>
       </c>
-      <c r="B113" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C113" s="5"/>
-      <c r="D113" s="5"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="5"/>
-      <c r="G113" s="5"/>
-      <c r="H113" s="5"/>
-    </row>
-    <row r="114" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="3" t="n">
+      <c r="B113" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="4"/>
+      <c r="H113" s="4"/>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="3">
         <v>44549</v>
       </c>
-      <c r="B114" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C114" s="5"/>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="5"/>
-      <c r="G114" s="5"/>
-      <c r="H114" s="5"/>
-    </row>
-    <row r="115" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="3" t="n">
+      <c r="B114" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C114" s="4"/>
+      <c r="D114" s="4"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="4"/>
+      <c r="H114" s="4"/>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" s="3">
         <v>44550</v>
       </c>
-      <c r="B115" s="4" t="n">
+      <c r="B115" s="4">
         <v>2</v>
       </c>
       <c r="C115" s="4" t="s">
@@ -2297,11 +3016,11 @@
       <c r="G115" s="4"/>
       <c r="H115" s="4"/>
     </row>
-    <row r="116" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="3" t="n">
+    <row r="116" spans="1:8">
+      <c r="A116" s="3">
         <v>44551</v>
       </c>
-      <c r="B116" s="4" t="n">
+      <c r="B116" s="4">
         <v>3</v>
       </c>
       <c r="C116" s="4" t="s">
@@ -2313,179 +3032,179 @@
       <c r="G116" s="4"/>
       <c r="H116" s="4"/>
     </row>
-    <row r="117" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="3" t="n">
+    <row r="117" spans="1:8">
+      <c r="A117" s="3">
         <v>44552</v>
       </c>
-      <c r="B117" s="9" t="s">
+      <c r="B117" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C117" s="9"/>
-      <c r="D117" s="9"/>
-      <c r="E117" s="9"/>
-      <c r="F117" s="9"/>
-      <c r="G117" s="9"/>
-      <c r="H117" s="9"/>
-    </row>
-    <row r="118" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="3" t="n">
+      <c r="C117" s="12"/>
+      <c r="D117" s="12"/>
+      <c r="E117" s="12"/>
+      <c r="F117" s="12"/>
+      <c r="G117" s="12"/>
+      <c r="H117" s="12"/>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" s="3">
         <v>44553</v>
       </c>
-      <c r="B118" s="9" t="s">
+      <c r="B118" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C118" s="9"/>
-      <c r="D118" s="9"/>
-      <c r="E118" s="9"/>
-      <c r="F118" s="9"/>
-      <c r="G118" s="9"/>
-      <c r="H118" s="9"/>
-    </row>
-    <row r="119" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="3" t="n">
+      <c r="C118" s="12"/>
+      <c r="D118" s="12"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="12"/>
+      <c r="H118" s="12"/>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="3">
         <v>44554</v>
       </c>
-      <c r="B119" s="9" t="s">
+      <c r="B119" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C119" s="9"/>
-      <c r="D119" s="9"/>
-      <c r="E119" s="9"/>
-      <c r="F119" s="9"/>
-      <c r="G119" s="9"/>
-      <c r="H119" s="9"/>
-    </row>
-    <row r="120" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="3" t="n">
+      <c r="C119" s="12"/>
+      <c r="D119" s="12"/>
+      <c r="E119" s="12"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="12"/>
+      <c r="H119" s="12"/>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" s="3">
         <v>44555</v>
       </c>
-      <c r="B120" s="9" t="s">
+      <c r="B120" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C120" s="9"/>
-      <c r="D120" s="9"/>
-      <c r="E120" s="9"/>
-      <c r="F120" s="9"/>
-      <c r="G120" s="9"/>
-      <c r="H120" s="9"/>
-    </row>
-    <row r="121" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="3" t="n">
+      <c r="C120" s="12"/>
+      <c r="D120" s="12"/>
+      <c r="E120" s="12"/>
+      <c r="F120" s="12"/>
+      <c r="G120" s="12"/>
+      <c r="H120" s="12"/>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" s="3">
         <v>44556</v>
       </c>
-      <c r="B121" s="9" t="s">
+      <c r="B121" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C121" s="9"/>
-      <c r="D121" s="9"/>
-      <c r="E121" s="9"/>
-      <c r="F121" s="9"/>
-      <c r="G121" s="9"/>
-      <c r="H121" s="9"/>
-    </row>
-    <row r="122" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="3" t="n">
+      <c r="C121" s="12"/>
+      <c r="D121" s="12"/>
+      <c r="E121" s="12"/>
+      <c r="F121" s="12"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="12"/>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" s="3">
         <v>44557</v>
       </c>
-      <c r="B122" s="9" t="s">
+      <c r="B122" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C122" s="9"/>
-      <c r="D122" s="9"/>
-      <c r="E122" s="9"/>
-      <c r="F122" s="9"/>
-      <c r="G122" s="9"/>
-      <c r="H122" s="9"/>
-    </row>
-    <row r="123" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="3" t="n">
+      <c r="C122" s="12"/>
+      <c r="D122" s="12"/>
+      <c r="E122" s="12"/>
+      <c r="F122" s="12"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" s="3">
         <v>44558</v>
       </c>
-      <c r="B123" s="9" t="s">
+      <c r="B123" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="9"/>
-      <c r="F123" s="9"/>
-      <c r="G123" s="9"/>
-      <c r="H123" s="9"/>
-    </row>
-    <row r="124" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="3" t="n">
+      <c r="C123" s="12"/>
+      <c r="D123" s="12"/>
+      <c r="E123" s="12"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" s="3">
         <v>44559</v>
       </c>
-      <c r="B124" s="9" t="s">
+      <c r="B124" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C124" s="9"/>
-      <c r="D124" s="9"/>
-      <c r="E124" s="9"/>
-      <c r="F124" s="9"/>
-      <c r="G124" s="9"/>
-      <c r="H124" s="9"/>
-    </row>
-    <row r="125" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="3" t="n">
+      <c r="C124" s="12"/>
+      <c r="D124" s="12"/>
+      <c r="E124" s="12"/>
+      <c r="F124" s="12"/>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="3">
         <v>44560</v>
       </c>
-      <c r="B125" s="9" t="s">
+      <c r="B125" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C125" s="9"/>
-      <c r="D125" s="9"/>
-      <c r="E125" s="9"/>
-      <c r="F125" s="9"/>
-      <c r="G125" s="9"/>
-      <c r="H125" s="9"/>
-    </row>
-    <row r="126" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="3" t="n">
+      <c r="C125" s="12"/>
+      <c r="D125" s="12"/>
+      <c r="E125" s="12"/>
+      <c r="F125" s="12"/>
+      <c r="G125" s="12"/>
+      <c r="H125" s="12"/>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="3">
         <v>44561</v>
       </c>
-      <c r="B126" s="9" t="s">
+      <c r="B126" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C126" s="9"/>
-      <c r="D126" s="9"/>
-      <c r="E126" s="9"/>
-      <c r="F126" s="9"/>
-      <c r="G126" s="9"/>
-      <c r="H126" s="9"/>
-    </row>
-    <row r="127" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="3" t="n">
+      <c r="C126" s="12"/>
+      <c r="D126" s="12"/>
+      <c r="E126" s="12"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="12"/>
+      <c r="H126" s="12"/>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="3">
         <v>44562</v>
       </c>
-      <c r="B127" s="9" t="s">
+      <c r="B127" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C127" s="9"/>
-      <c r="D127" s="9"/>
-      <c r="E127" s="9"/>
-      <c r="F127" s="9"/>
-      <c r="G127" s="9"/>
-      <c r="H127" s="9"/>
-    </row>
-    <row r="128" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="3" t="n">
+      <c r="C127" s="12"/>
+      <c r="D127" s="12"/>
+      <c r="E127" s="12"/>
+      <c r="F127" s="12"/>
+      <c r="G127" s="12"/>
+      <c r="H127" s="12"/>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="3">
         <v>44563</v>
       </c>
-      <c r="B128" s="9" t="s">
+      <c r="B128" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C128" s="9"/>
-      <c r="D128" s="9"/>
-      <c r="E128" s="9"/>
-      <c r="F128" s="9"/>
-      <c r="G128" s="9"/>
-      <c r="H128" s="9"/>
-    </row>
-    <row r="129" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="3" t="n">
+      <c r="C128" s="12"/>
+      <c r="D128" s="12"/>
+      <c r="E128" s="12"/>
+      <c r="F128" s="12"/>
+      <c r="G128" s="12"/>
+      <c r="H128" s="12"/>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" s="3">
         <v>44564</v>
       </c>
-      <c r="B129" s="4" t="n">
+      <c r="B129" s="4">
         <v>4</v>
       </c>
       <c r="C129" s="4" t="s">
@@ -2497,11 +3216,11 @@
       <c r="G129" s="4"/>
       <c r="H129" s="4"/>
     </row>
-    <row r="130" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="3" t="n">
+    <row r="130" spans="1:8">
+      <c r="A130" s="3">
         <v>44565</v>
       </c>
-      <c r="B130" s="4" t="n">
+      <c r="B130" s="4">
         <v>5</v>
       </c>
       <c r="C130" s="4" t="s">
@@ -2513,11 +3232,11 @@
       <c r="G130" s="4"/>
       <c r="H130" s="4"/>
     </row>
-    <row r="131" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="3" t="n">
+    <row r="131" spans="1:8">
+      <c r="A131" s="3">
         <v>44566</v>
       </c>
-      <c r="B131" s="4" t="n">
+      <c r="B131" s="4">
         <v>6</v>
       </c>
       <c r="C131" s="4" t="s">
@@ -2529,11 +3248,11 @@
       <c r="G131" s="4"/>
       <c r="H131" s="4"/>
     </row>
-    <row r="132" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="3" t="n">
+    <row r="132" spans="1:8">
+      <c r="A132" s="3">
         <v>44567</v>
       </c>
-      <c r="B132" s="4" t="n">
+      <c r="B132" s="4">
         <v>7</v>
       </c>
       <c r="C132" s="4" t="s">
@@ -2545,11 +3264,11 @@
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
     </row>
-    <row r="133" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="3" t="n">
+    <row r="133" spans="1:8">
+      <c r="A133" s="3">
         <v>44568</v>
       </c>
-      <c r="B133" s="4" t="n">
+      <c r="B133" s="4">
         <v>1</v>
       </c>
       <c r="C133" s="4" t="s">
@@ -2561,39 +3280,39 @@
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
     </row>
-    <row r="134" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="3" t="n">
+    <row r="134" spans="1:8">
+      <c r="A134" s="3">
         <v>44569</v>
       </c>
-      <c r="B134" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C134" s="5"/>
-      <c r="D134" s="5"/>
-      <c r="E134" s="5"/>
-      <c r="F134" s="5"/>
-      <c r="G134" s="5"/>
-      <c r="H134" s="5"/>
-    </row>
-    <row r="135" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="3" t="n">
+      <c r="B134" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C134" s="4"/>
+      <c r="D134" s="4"/>
+      <c r="E134" s="4"/>
+      <c r="F134" s="4"/>
+      <c r="G134" s="4"/>
+      <c r="H134" s="4"/>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" s="3">
         <v>44570</v>
       </c>
-      <c r="B135" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C135" s="5"/>
-      <c r="D135" s="5"/>
-      <c r="E135" s="5"/>
-      <c r="F135" s="5"/>
-      <c r="G135" s="5"/>
-      <c r="H135" s="5"/>
-    </row>
-    <row r="136" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="3" t="n">
+      <c r="B135" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4"/>
+      <c r="E135" s="4"/>
+      <c r="F135" s="4"/>
+      <c r="G135" s="4"/>
+      <c r="H135" s="4"/>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" s="3">
         <v>44571</v>
       </c>
-      <c r="B136" s="4" t="n">
+      <c r="B136" s="4">
         <v>2</v>
       </c>
       <c r="C136" s="4" t="s">
@@ -2605,11 +3324,11 @@
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
     </row>
-    <row r="137" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="3" t="n">
+    <row r="137" spans="1:8">
+      <c r="A137" s="3">
         <v>44572</v>
       </c>
-      <c r="B137" s="4" t="n">
+      <c r="B137" s="4">
         <v>3</v>
       </c>
       <c r="C137" s="4" t="s">
@@ -2621,11 +3340,11 @@
       <c r="G137" s="4"/>
       <c r="H137" s="4"/>
     </row>
-    <row r="138" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="3" t="n">
+    <row r="138" spans="1:8">
+      <c r="A138" s="3">
         <v>44573</v>
       </c>
-      <c r="B138" s="4" t="n">
+      <c r="B138" s="4">
         <v>4</v>
       </c>
       <c r="C138" s="4" t="s">
@@ -2637,11 +3356,11 @@
       <c r="G138" s="4"/>
       <c r="H138" s="4"/>
     </row>
-    <row r="139" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="3" t="n">
+    <row r="139" spans="1:8">
+      <c r="A139" s="3">
         <v>44574</v>
       </c>
-      <c r="B139" s="4" t="n">
+      <c r="B139" s="4">
         <v>5</v>
       </c>
       <c r="C139" s="4" t="s">
@@ -2653,11 +3372,11 @@
       <c r="G139" s="4"/>
       <c r="H139" s="4"/>
     </row>
-    <row r="140" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="3" t="n">
+    <row r="140" spans="1:8">
+      <c r="A140" s="3">
         <v>44575</v>
       </c>
-      <c r="B140" s="4" t="n">
+      <c r="B140" s="4">
         <v>6</v>
       </c>
       <c r="C140" s="4" t="s">
@@ -2669,39 +3388,39 @@
       <c r="G140" s="4"/>
       <c r="H140" s="4"/>
     </row>
-    <row r="141" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="3" t="n">
+    <row r="141" spans="1:8">
+      <c r="A141" s="3">
         <v>44576</v>
       </c>
-      <c r="B141" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C141" s="5"/>
-      <c r="D141" s="5"/>
-      <c r="E141" s="5"/>
-      <c r="F141" s="5"/>
-      <c r="G141" s="5"/>
-      <c r="H141" s="5"/>
-    </row>
-    <row r="142" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="3" t="n">
+      <c r="B141" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="4"/>
+      <c r="F141" s="4"/>
+      <c r="G141" s="4"/>
+      <c r="H141" s="4"/>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" s="3">
         <v>44577</v>
       </c>
-      <c r="B142" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C142" s="5"/>
-      <c r="D142" s="5"/>
-      <c r="E142" s="5"/>
-      <c r="F142" s="5"/>
-      <c r="G142" s="5"/>
-      <c r="H142" s="5"/>
-    </row>
-    <row r="143" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="3" t="n">
+      <c r="B142" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="4"/>
+      <c r="F142" s="4"/>
+      <c r="G142" s="4"/>
+      <c r="H142" s="4"/>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" s="3">
         <v>44578</v>
       </c>
-      <c r="B143" s="4" t="n">
+      <c r="B143" s="4">
         <v>7</v>
       </c>
       <c r="C143" s="4" t="s">
@@ -2713,11 +3432,11 @@
       <c r="G143" s="4"/>
       <c r="H143" s="4"/>
     </row>
-    <row r="144" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="3" t="n">
+    <row r="144" spans="1:8">
+      <c r="A144" s="3">
         <v>44579</v>
       </c>
-      <c r="B144" s="4" t="n">
+      <c r="B144" s="4">
         <v>1</v>
       </c>
       <c r="C144" s="4" t="s">
@@ -2729,11 +3448,11 @@
       <c r="G144" s="4"/>
       <c r="H144" s="4"/>
     </row>
-    <row r="145" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="3" t="n">
+    <row r="145" spans="1:8">
+      <c r="A145" s="3">
         <v>44580</v>
       </c>
-      <c r="B145" s="4" t="n">
+      <c r="B145" s="4">
         <v>2</v>
       </c>
       <c r="C145" s="4" t="s">
@@ -2745,11 +3464,11 @@
       <c r="G145" s="4"/>
       <c r="H145" s="4"/>
     </row>
-    <row r="146" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="3" t="n">
+    <row r="146" spans="1:8">
+      <c r="A146" s="3">
         <v>44581</v>
       </c>
-      <c r="B146" s="4" t="n">
+      <c r="B146" s="4">
         <v>3</v>
       </c>
       <c r="C146" s="4" t="s">
@@ -2761,11 +3480,11 @@
       <c r="G146" s="4"/>
       <c r="H146" s="4"/>
     </row>
-    <row r="147" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="3" t="n">
+    <row r="147" spans="1:8">
+      <c r="A147" s="3">
         <v>44582</v>
       </c>
-      <c r="B147" s="4" t="n">
+      <c r="B147" s="4">
         <v>4</v>
       </c>
       <c r="C147" s="4" t="s">
@@ -2777,39 +3496,39 @@
       <c r="G147" s="4"/>
       <c r="H147" s="4"/>
     </row>
-    <row r="148" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="3" t="n">
+    <row r="148" spans="1:8">
+      <c r="A148" s="3">
         <v>44583</v>
       </c>
-      <c r="B148" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C148" s="5"/>
-      <c r="D148" s="5"/>
-      <c r="E148" s="5"/>
-      <c r="F148" s="5"/>
-      <c r="G148" s="5"/>
-      <c r="H148" s="5"/>
-    </row>
-    <row r="149" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="3" t="n">
+      <c r="B148" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C148" s="4"/>
+      <c r="D148" s="4"/>
+      <c r="E148" s="4"/>
+      <c r="F148" s="4"/>
+      <c r="G148" s="4"/>
+      <c r="H148" s="4"/>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="3">
         <v>44584</v>
       </c>
-      <c r="B149" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C149" s="5"/>
-      <c r="D149" s="5"/>
-      <c r="E149" s="5"/>
-      <c r="F149" s="5"/>
-      <c r="G149" s="5"/>
-      <c r="H149" s="5"/>
-    </row>
-    <row r="150" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="3" t="n">
+      <c r="B149" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C149" s="4"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="4"/>
+      <c r="G149" s="4"/>
+      <c r="H149" s="4"/>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="A150" s="3">
         <v>44585</v>
       </c>
-      <c r="B150" s="4" t="n">
+      <c r="B150" s="4">
         <v>5</v>
       </c>
       <c r="C150" s="4" t="s">
@@ -2820,15 +3539,15 @@
       <c r="F150" s="4"/>
       <c r="G150" s="4"/>
       <c r="H150" s="4"/>
-      <c r="J150" s="10" t="s">
+      <c r="J150" s="13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="3" t="n">
+    <row r="151" spans="1:8">
+      <c r="A151" s="3">
         <v>44586</v>
       </c>
-      <c r="B151" s="4" t="n">
+      <c r="B151" s="4">
         <v>6</v>
       </c>
       <c r="C151" s="4" t="s">
@@ -2840,11 +3559,11 @@
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
     </row>
-    <row r="152" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="3" t="n">
+    <row r="152" spans="1:8">
+      <c r="A152" s="3">
         <v>44587</v>
       </c>
-      <c r="B152" s="4" t="n">
+      <c r="B152" s="4">
         <v>7</v>
       </c>
       <c r="C152" s="4" t="s">
@@ -2856,11 +3575,11 @@
       <c r="G152" s="4"/>
       <c r="H152" s="4"/>
     </row>
-    <row r="153" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="3" t="n">
+    <row r="153" spans="1:8">
+      <c r="A153" s="3">
         <v>44588</v>
       </c>
-      <c r="B153" s="4" t="n">
+      <c r="B153" s="4">
         <v>1</v>
       </c>
       <c r="C153" s="4" t="s">
@@ -2872,11 +3591,11 @@
       <c r="G153" s="4"/>
       <c r="H153" s="4"/>
     </row>
-    <row r="154" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="3" t="n">
+    <row r="154" spans="1:8">
+      <c r="A154" s="3">
         <v>44589</v>
       </c>
-      <c r="B154" s="4" t="n">
+      <c r="B154" s="4">
         <v>2</v>
       </c>
       <c r="C154" s="4" t="s">
@@ -2888,39 +3607,39 @@
       <c r="G154" s="4"/>
       <c r="H154" s="4"/>
     </row>
-    <row r="155" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="3" t="n">
+    <row r="155" spans="1:8">
+      <c r="A155" s="3">
         <v>44590</v>
       </c>
-      <c r="B155" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C155" s="5"/>
-      <c r="D155" s="5"/>
-      <c r="E155" s="5"/>
-      <c r="F155" s="5"/>
-      <c r="G155" s="5"/>
-      <c r="H155" s="5"/>
-    </row>
-    <row r="156" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="3" t="n">
+      <c r="B155" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C155" s="4"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="4"/>
+      <c r="G155" s="4"/>
+      <c r="H155" s="4"/>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" s="3">
         <v>44591</v>
       </c>
-      <c r="B156" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C156" s="5"/>
-      <c r="D156" s="5"/>
-      <c r="E156" s="5"/>
-      <c r="F156" s="5"/>
-      <c r="G156" s="5"/>
-      <c r="H156" s="5"/>
-    </row>
-    <row r="157" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="3" t="n">
+      <c r="B156" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C156" s="4"/>
+      <c r="D156" s="4"/>
+      <c r="E156" s="4"/>
+      <c r="F156" s="4"/>
+      <c r="G156" s="4"/>
+      <c r="H156" s="4"/>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" s="3">
         <v>44592</v>
       </c>
-      <c r="B157" s="4" t="n">
+      <c r="B157" s="4">
         <v>3</v>
       </c>
       <c r="C157" s="4" t="s">
@@ -2932,11 +3651,11 @@
       <c r="G157" s="4"/>
       <c r="H157" s="4"/>
     </row>
-    <row r="158" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="3" t="n">
+    <row r="158" spans="1:8">
+      <c r="A158" s="3">
         <v>44593</v>
       </c>
-      <c r="B158" s="4" t="n">
+      <c r="B158" s="4">
         <v>4</v>
       </c>
       <c r="C158" s="4" t="s">
@@ -2948,11 +3667,11 @@
       <c r="G158" s="4"/>
       <c r="H158" s="4"/>
     </row>
-    <row r="159" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="3" t="n">
+    <row r="159" spans="1:8">
+      <c r="A159" s="3">
         <v>44594</v>
       </c>
-      <c r="B159" s="4" t="n">
+      <c r="B159" s="4">
         <v>5</v>
       </c>
       <c r="C159" s="4" t="s">
@@ -2964,11 +3683,11 @@
       <c r="G159" s="4"/>
       <c r="H159" s="4"/>
     </row>
-    <row r="160" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="3" t="n">
+    <row r="160" spans="1:8">
+      <c r="A160" s="3">
         <v>44595</v>
       </c>
-      <c r="B160" s="4" t="n">
+      <c r="B160" s="4">
         <v>6</v>
       </c>
       <c r="C160" s="4" t="s">
@@ -2980,11 +3699,11 @@
       <c r="G160" s="4"/>
       <c r="H160" s="4"/>
     </row>
-    <row r="161" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="3" t="n">
+    <row r="161" spans="1:8">
+      <c r="A161" s="3">
         <v>44596</v>
       </c>
-      <c r="B161" s="4" t="n">
+      <c r="B161" s="4">
         <v>7</v>
       </c>
       <c r="C161" s="4" t="s">
@@ -2996,39 +3715,39 @@
       <c r="G161" s="4"/>
       <c r="H161" s="4"/>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="3" t="n">
+    <row r="162" ht="15" customHeight="1" spans="1:8">
+      <c r="A162" s="3">
         <v>44597</v>
       </c>
-      <c r="B162" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C162" s="5"/>
-      <c r="D162" s="5"/>
-      <c r="E162" s="5"/>
-      <c r="F162" s="5"/>
-      <c r="G162" s="5"/>
-      <c r="H162" s="5"/>
-    </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="3" t="n">
+      <c r="B162" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C162" s="4"/>
+      <c r="D162" s="4"/>
+      <c r="E162" s="4"/>
+      <c r="F162" s="4"/>
+      <c r="G162" s="4"/>
+      <c r="H162" s="4"/>
+    </row>
+    <row r="163" ht="15" customHeight="1" spans="1:8">
+      <c r="A163" s="3">
         <v>44598</v>
       </c>
-      <c r="B163" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C163" s="5"/>
-      <c r="D163" s="5"/>
-      <c r="E163" s="5"/>
-      <c r="F163" s="5"/>
-      <c r="G163" s="5"/>
-      <c r="H163" s="5"/>
-    </row>
-    <row r="164" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="3" t="n">
+      <c r="B163" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C163" s="4"/>
+      <c r="D163" s="4"/>
+      <c r="E163" s="4"/>
+      <c r="F163" s="4"/>
+      <c r="G163" s="4"/>
+      <c r="H163" s="4"/>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164" s="3">
         <v>44599</v>
       </c>
-      <c r="B164" s="4" t="n">
+      <c r="B164" s="4">
         <v>1</v>
       </c>
       <c r="C164" s="4" t="s">
@@ -3040,11 +3759,11 @@
       <c r="G164" s="4"/>
       <c r="H164" s="4"/>
     </row>
-    <row r="165" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="3" t="n">
+    <row r="165" spans="1:8">
+      <c r="A165" s="3">
         <v>44600</v>
       </c>
-      <c r="B165" s="4" t="n">
+      <c r="B165" s="4">
         <v>2</v>
       </c>
       <c r="C165" s="4" t="s">
@@ -3056,11 +3775,11 @@
       <c r="G165" s="4"/>
       <c r="H165" s="4"/>
     </row>
-    <row r="166" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="3" t="n">
+    <row r="166" spans="1:8">
+      <c r="A166" s="3">
         <v>44601</v>
       </c>
-      <c r="B166" s="4" t="n">
+      <c r="B166" s="4">
         <v>3</v>
       </c>
       <c r="C166" s="4" t="s">
@@ -3072,11 +3791,11 @@
       <c r="G166" s="4"/>
       <c r="H166" s="4"/>
     </row>
-    <row r="167" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="3" t="n">
+    <row r="167" spans="1:8">
+      <c r="A167" s="3">
         <v>44602</v>
       </c>
-      <c r="B167" s="4" t="n">
+      <c r="B167" s="4">
         <v>4</v>
       </c>
       <c r="C167" s="4" t="s">
@@ -3088,11 +3807,11 @@
       <c r="G167" s="4"/>
       <c r="H167" s="4"/>
     </row>
-    <row r="168" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="3" t="n">
+    <row r="168" spans="1:8">
+      <c r="A168" s="3">
         <v>44603</v>
       </c>
-      <c r="B168" s="4" t="n">
+      <c r="B168" s="4">
         <v>5</v>
       </c>
       <c r="C168" s="4" t="s">
@@ -3104,39 +3823,39 @@
       <c r="G168" s="4"/>
       <c r="H168" s="4"/>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="3" t="n">
+    <row r="169" ht="15" customHeight="1" spans="1:8">
+      <c r="A169" s="3">
         <v>44604</v>
       </c>
-      <c r="B169" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C169" s="5"/>
-      <c r="D169" s="5"/>
-      <c r="E169" s="5"/>
-      <c r="F169" s="5"/>
-      <c r="G169" s="5"/>
-      <c r="H169" s="5"/>
-    </row>
-    <row r="170" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="3" t="n">
+      <c r="B169" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C169" s="4"/>
+      <c r="D169" s="4"/>
+      <c r="E169" s="4"/>
+      <c r="F169" s="4"/>
+      <c r="G169" s="4"/>
+      <c r="H169" s="4"/>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" s="3">
         <v>44605</v>
       </c>
-      <c r="B170" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C170" s="5"/>
-      <c r="D170" s="5"/>
-      <c r="E170" s="5"/>
-      <c r="F170" s="5"/>
-      <c r="G170" s="5"/>
-      <c r="H170" s="5"/>
-    </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="3" t="n">
+      <c r="B170" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C170" s="4"/>
+      <c r="D170" s="4"/>
+      <c r="E170" s="4"/>
+      <c r="F170" s="4"/>
+      <c r="G170" s="4"/>
+      <c r="H170" s="4"/>
+    </row>
+    <row r="171" ht="15" customHeight="1" spans="1:8">
+      <c r="A171" s="3">
         <v>44606</v>
       </c>
-      <c r="B171" s="4" t="n">
+      <c r="B171" s="4">
         <v>6</v>
       </c>
       <c r="C171" s="4" t="s">
@@ -3148,11 +3867,11 @@
       <c r="G171" s="4"/>
       <c r="H171" s="4"/>
     </row>
-    <row r="172" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="3" t="n">
+    <row r="172" spans="1:8">
+      <c r="A172" s="3">
         <v>44607</v>
       </c>
-      <c r="B172" s="4" t="n">
+      <c r="B172" s="4">
         <v>7</v>
       </c>
       <c r="C172" s="4" t="s">
@@ -3164,11 +3883,11 @@
       <c r="G172" s="4"/>
       <c r="H172" s="4"/>
     </row>
-    <row r="173" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="3" t="n">
+    <row r="173" spans="1:8">
+      <c r="A173" s="3">
         <v>44608</v>
       </c>
-      <c r="B173" s="4" t="n">
+      <c r="B173" s="4">
         <v>1</v>
       </c>
       <c r="C173" s="4" t="s">
@@ -3180,11 +3899,11 @@
       <c r="G173" s="4"/>
       <c r="H173" s="4"/>
     </row>
-    <row r="174" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="3" t="n">
+    <row r="174" spans="1:8">
+      <c r="A174" s="3">
         <v>44609</v>
       </c>
-      <c r="B174" s="4" t="n">
+      <c r="B174" s="4">
         <v>2</v>
       </c>
       <c r="C174" s="4" t="s">
@@ -3196,11 +3915,11 @@
       <c r="G174" s="4"/>
       <c r="H174" s="4"/>
     </row>
-    <row r="175" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="3" t="n">
+    <row r="175" spans="1:8">
+      <c r="A175" s="3">
         <v>44610</v>
       </c>
-      <c r="B175" s="4" t="n">
+      <c r="B175" s="4">
         <v>3</v>
       </c>
       <c r="C175" s="4" t="s">
@@ -3212,39 +3931,39 @@
       <c r="G175" s="4"/>
       <c r="H175" s="4"/>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="3" t="n">
+    <row r="176" ht="15" customHeight="1" spans="1:8">
+      <c r="A176" s="3">
         <v>44611</v>
       </c>
-      <c r="B176" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C176" s="5"/>
-      <c r="D176" s="5"/>
-      <c r="E176" s="5"/>
-      <c r="F176" s="5"/>
-      <c r="G176" s="5"/>
-      <c r="H176" s="5"/>
-    </row>
-    <row r="177" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="3" t="n">
+      <c r="B176" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C176" s="4"/>
+      <c r="D176" s="4"/>
+      <c r="E176" s="4"/>
+      <c r="F176" s="4"/>
+      <c r="G176" s="4"/>
+      <c r="H176" s="4"/>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" s="3">
         <v>44612</v>
       </c>
       <c r="B177" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C177" s="5"/>
-      <c r="D177" s="5"/>
-      <c r="E177" s="5"/>
-      <c r="F177" s="5"/>
-      <c r="G177" s="5"/>
-      <c r="H177" s="5"/>
-    </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="3" t="n">
+      <c r="C177" s="14"/>
+      <c r="D177" s="14"/>
+      <c r="E177" s="14"/>
+      <c r="F177" s="14"/>
+      <c r="G177" s="14"/>
+      <c r="H177" s="6"/>
+    </row>
+    <row r="178" ht="15" customHeight="1" spans="1:8">
+      <c r="A178" s="3">
         <v>44613</v>
       </c>
-      <c r="B178" s="4" t="n">
+      <c r="B178" s="4">
         <v>4</v>
       </c>
       <c r="C178" s="4" t="s">
@@ -3256,11 +3975,11 @@
       <c r="G178" s="4"/>
       <c r="H178" s="4"/>
     </row>
-    <row r="179" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="3" t="n">
+    <row r="179" spans="1:8">
+      <c r="A179" s="3">
         <v>44614</v>
       </c>
-      <c r="B179" s="4" t="n">
+      <c r="B179" s="4">
         <v>5</v>
       </c>
       <c r="C179" s="4" t="s">
@@ -3272,11 +3991,11 @@
       <c r="G179" s="4"/>
       <c r="H179" s="4"/>
     </row>
-    <row r="180" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="3" t="n">
+    <row r="180" spans="1:8">
+      <c r="A180" s="3">
         <v>44615</v>
       </c>
-      <c r="B180" s="4" t="n">
+      <c r="B180" s="4">
         <v>6</v>
       </c>
       <c r="C180" s="4" t="s">
@@ -3288,11 +4007,11 @@
       <c r="G180" s="4"/>
       <c r="H180" s="4"/>
     </row>
-    <row r="181" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="3" t="n">
+    <row r="181" spans="1:8">
+      <c r="A181" s="3">
         <v>44616</v>
       </c>
-      <c r="B181" s="4" t="n">
+      <c r="B181" s="4">
         <v>7</v>
       </c>
       <c r="C181" s="4" t="s">
@@ -3304,11 +4023,11 @@
       <c r="G181" s="4"/>
       <c r="H181" s="4"/>
     </row>
-    <row r="182" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="3" t="n">
+    <row r="182" spans="1:8">
+      <c r="A182" s="3">
         <v>44617</v>
       </c>
-      <c r="B182" s="4" t="n">
+      <c r="B182" s="4">
         <v>1</v>
       </c>
       <c r="C182" s="4" t="s">
@@ -3320,39 +4039,39 @@
       <c r="G182" s="4"/>
       <c r="H182" s="4"/>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="3" t="n">
+    <row r="183" ht="15" customHeight="1" spans="1:8">
+      <c r="A183" s="3">
         <v>44618</v>
       </c>
-      <c r="B183" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C183" s="5"/>
-      <c r="D183" s="5"/>
-      <c r="E183" s="5"/>
-      <c r="F183" s="5"/>
-      <c r="G183" s="5"/>
-      <c r="H183" s="5"/>
-    </row>
-    <row r="184" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="3" t="n">
+      <c r="B183" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C183" s="4"/>
+      <c r="D183" s="4"/>
+      <c r="E183" s="4"/>
+      <c r="F183" s="4"/>
+      <c r="G183" s="4"/>
+      <c r="H183" s="4"/>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184" s="3">
         <v>44619</v>
       </c>
       <c r="B184" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C184" s="5"/>
-      <c r="D184" s="5"/>
-      <c r="E184" s="5"/>
-      <c r="F184" s="5"/>
-      <c r="G184" s="5"/>
-      <c r="H184" s="5"/>
-    </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="3" t="n">
+      <c r="C184" s="14"/>
+      <c r="D184" s="14"/>
+      <c r="E184" s="14"/>
+      <c r="F184" s="14"/>
+      <c r="G184" s="14"/>
+      <c r="H184" s="6"/>
+    </row>
+    <row r="185" ht="15" customHeight="1" spans="1:8">
+      <c r="A185" s="3">
         <v>44620</v>
       </c>
-      <c r="B185" s="4" t="n">
+      <c r="B185" s="4">
         <v>2</v>
       </c>
       <c r="C185" s="4" t="s">
@@ -3364,11 +4083,11 @@
       <c r="G185" s="4"/>
       <c r="H185" s="4"/>
     </row>
-    <row r="186" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="3" t="n">
+    <row r="186" spans="1:8">
+      <c r="A186" s="3">
         <v>44621</v>
       </c>
-      <c r="B186" s="4" t="n">
+      <c r="B186" s="4">
         <v>3</v>
       </c>
       <c r="C186" s="4" t="s">
@@ -3380,11 +4099,11 @@
       <c r="G186" s="4"/>
       <c r="H186" s="4"/>
     </row>
-    <row r="187" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="3" t="n">
+    <row r="187" spans="1:8">
+      <c r="A187" s="3">
         <v>44622</v>
       </c>
-      <c r="B187" s="4" t="n">
+      <c r="B187" s="4">
         <v>4</v>
       </c>
       <c r="C187" s="4" t="s">
@@ -3396,11 +4115,11 @@
       <c r="G187" s="4"/>
       <c r="H187" s="4"/>
     </row>
-    <row r="188" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="3" t="n">
+    <row r="188" spans="1:8">
+      <c r="A188" s="3">
         <v>44623</v>
       </c>
-      <c r="B188" s="4" t="n">
+      <c r="B188" s="4">
         <v>5</v>
       </c>
       <c r="C188" s="4" t="s">
@@ -3412,11 +4131,11 @@
       <c r="G188" s="4"/>
       <c r="H188" s="4"/>
     </row>
-    <row r="189" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="3" t="n">
+    <row r="189" spans="1:8">
+      <c r="A189" s="3">
         <v>44624</v>
       </c>
-      <c r="B189" s="4" t="n">
+      <c r="B189" s="4">
         <v>6</v>
       </c>
       <c r="C189" s="4" t="s">
@@ -3428,39 +4147,39 @@
       <c r="G189" s="4"/>
       <c r="H189" s="4"/>
     </row>
-    <row r="190" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="3" t="n">
+    <row r="190" spans="1:8">
+      <c r="A190" s="3">
         <v>44625</v>
       </c>
-      <c r="B190" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C190" s="5"/>
-      <c r="D190" s="5"/>
-      <c r="E190" s="5"/>
-      <c r="F190" s="5"/>
-      <c r="G190" s="5"/>
-      <c r="H190" s="5"/>
-    </row>
-    <row r="191" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="3" t="n">
+      <c r="B190" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C190" s="4"/>
+      <c r="D190" s="4"/>
+      <c r="E190" s="4"/>
+      <c r="F190" s="4"/>
+      <c r="G190" s="4"/>
+      <c r="H190" s="4"/>
+    </row>
+    <row r="191" spans="1:8">
+      <c r="A191" s="3">
         <v>44626</v>
       </c>
       <c r="B191" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C191" s="5"/>
-      <c r="D191" s="5"/>
-      <c r="E191" s="5"/>
-      <c r="F191" s="5"/>
-      <c r="G191" s="5"/>
-      <c r="H191" s="5"/>
-    </row>
-    <row r="192" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="3" t="n">
+      <c r="C191" s="14"/>
+      <c r="D191" s="14"/>
+      <c r="E191" s="14"/>
+      <c r="F191" s="14"/>
+      <c r="G191" s="14"/>
+      <c r="H191" s="6"/>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192" s="3">
         <v>44627</v>
       </c>
-      <c r="B192" s="4" t="n">
+      <c r="B192" s="4">
         <v>7</v>
       </c>
       <c r="C192" s="4" t="s">
@@ -3472,11 +4191,11 @@
       <c r="G192" s="4"/>
       <c r="H192" s="4"/>
     </row>
-    <row r="193" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="3" t="n">
+    <row r="193" spans="1:8">
+      <c r="A193" s="3">
         <v>44628</v>
       </c>
-      <c r="B193" s="4" t="n">
+      <c r="B193" s="4">
         <v>1</v>
       </c>
       <c r="C193" s="4" t="s">
@@ -3488,11 +4207,11 @@
       <c r="G193" s="4"/>
       <c r="H193" s="4"/>
     </row>
-    <row r="194" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="3" t="n">
+    <row r="194" spans="1:8">
+      <c r="A194" s="3">
         <v>44629</v>
       </c>
-      <c r="B194" s="4" t="n">
+      <c r="B194" s="4">
         <v>2</v>
       </c>
       <c r="C194" s="4" t="s">
@@ -3504,11 +4223,11 @@
       <c r="G194" s="4"/>
       <c r="H194" s="4"/>
     </row>
-    <row r="195" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="3" t="n">
+    <row r="195" spans="1:8">
+      <c r="A195" s="3">
         <v>44630</v>
       </c>
-      <c r="B195" s="4" t="n">
+      <c r="B195" s="4">
         <v>3</v>
       </c>
       <c r="C195" s="4" t="s">
@@ -3520,11 +4239,11 @@
       <c r="G195" s="4"/>
       <c r="H195" s="4"/>
     </row>
-    <row r="196" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="3" t="n">
+    <row r="196" spans="1:8">
+      <c r="A196" s="3">
         <v>44631</v>
       </c>
-      <c r="B196" s="4" t="n">
+      <c r="B196" s="4">
         <v>4</v>
       </c>
       <c r="C196" s="4" t="s">
@@ -3536,53 +4255,53 @@
       <c r="G196" s="4"/>
       <c r="H196" s="4"/>
     </row>
-    <row r="197" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="3" t="n">
+    <row r="197" spans="1:8">
+      <c r="A197" s="3">
         <v>44632</v>
       </c>
-      <c r="B197" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C197" s="5"/>
-      <c r="D197" s="5"/>
-      <c r="E197" s="5"/>
-      <c r="F197" s="5"/>
-      <c r="G197" s="5"/>
-      <c r="H197" s="5"/>
-    </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="3" t="n">
+      <c r="B197" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C197" s="4"/>
+      <c r="D197" s="4"/>
+      <c r="E197" s="4"/>
+      <c r="F197" s="4"/>
+      <c r="G197" s="4"/>
+      <c r="H197" s="4"/>
+    </row>
+    <row r="198" ht="15" customHeight="1" spans="1:8">
+      <c r="A198" s="3">
         <v>44633</v>
       </c>
-      <c r="B198" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C198" s="5"/>
-      <c r="D198" s="5"/>
-      <c r="E198" s="5"/>
-      <c r="F198" s="5"/>
-      <c r="G198" s="5"/>
-      <c r="H198" s="5"/>
-    </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="3" t="n">
+      <c r="B198" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C198" s="4"/>
+      <c r="D198" s="4"/>
+      <c r="E198" s="4"/>
+      <c r="F198" s="4"/>
+      <c r="G198" s="4"/>
+      <c r="H198" s="4"/>
+    </row>
+    <row r="199" ht="15" customHeight="1" spans="1:8">
+      <c r="A199" s="3">
         <v>44634</v>
       </c>
-      <c r="B199" s="9" t="s">
+      <c r="B199" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C199" s="9"/>
-      <c r="D199" s="9"/>
-      <c r="E199" s="9"/>
-      <c r="F199" s="9"/>
-      <c r="G199" s="9"/>
-      <c r="H199" s="9"/>
-    </row>
-    <row r="200" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="3" t="n">
+      <c r="C199" s="12"/>
+      <c r="D199" s="12"/>
+      <c r="E199" s="12"/>
+      <c r="F199" s="12"/>
+      <c r="G199" s="12"/>
+      <c r="H199" s="12"/>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200" s="3">
         <v>44635</v>
       </c>
-      <c r="B200" s="4" t="n">
+      <c r="B200" s="4">
         <v>6</v>
       </c>
       <c r="C200" s="4" t="s">
@@ -3594,11 +4313,11 @@
       <c r="G200" s="4"/>
       <c r="H200" s="4"/>
     </row>
-    <row r="201" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="3" t="n">
+    <row r="201" spans="1:8">
+      <c r="A201" s="3">
         <v>44636</v>
       </c>
-      <c r="B201" s="4" t="n">
+      <c r="B201" s="4">
         <v>7</v>
       </c>
       <c r="C201" s="4" t="s">
@@ -3610,11 +4329,11 @@
       <c r="G201" s="4"/>
       <c r="H201" s="4"/>
     </row>
-    <row r="202" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="3" t="n">
+    <row r="202" spans="1:10">
+      <c r="A202" s="3">
         <v>44637</v>
       </c>
-      <c r="B202" s="4" t="n">
+      <c r="B202" s="4">
         <v>1</v>
       </c>
       <c r="C202" s="4" t="s">
@@ -3625,13 +4344,13 @@
       <c r="F202" s="4"/>
       <c r="G202" s="4"/>
       <c r="H202" s="4"/>
-      <c r="J202" s="10"/>
-    </row>
-    <row r="203" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="3" t="n">
+      <c r="J202" s="13"/>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" s="3">
         <v>44638</v>
       </c>
-      <c r="B203" s="4" t="n">
+      <c r="B203" s="4">
         <v>2</v>
       </c>
       <c r="C203" s="4" t="s">
@@ -3643,39 +4362,39 @@
       <c r="G203" s="4"/>
       <c r="H203" s="4"/>
     </row>
-    <row r="204" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A204" s="3" t="n">
+    <row r="204" spans="1:8">
+      <c r="A204" s="3">
         <v>44639</v>
       </c>
       <c r="B204" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C204" s="5"/>
-      <c r="D204" s="5"/>
-      <c r="E204" s="5"/>
-      <c r="F204" s="5"/>
-      <c r="G204" s="5"/>
-      <c r="H204" s="5"/>
-    </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A205" s="3" t="n">
+      <c r="C204" s="14"/>
+      <c r="D204" s="14"/>
+      <c r="E204" s="14"/>
+      <c r="F204" s="14"/>
+      <c r="G204" s="14"/>
+      <c r="H204" s="6"/>
+    </row>
+    <row r="205" ht="15" customHeight="1" spans="1:8">
+      <c r="A205" s="3">
         <v>44640</v>
       </c>
       <c r="B205" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C205" s="5"/>
-      <c r="D205" s="5"/>
-      <c r="E205" s="5"/>
-      <c r="F205" s="5"/>
-      <c r="G205" s="5"/>
-      <c r="H205" s="5"/>
-    </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A206" s="3" t="n">
+      <c r="C205" s="14"/>
+      <c r="D205" s="14"/>
+      <c r="E205" s="14"/>
+      <c r="F205" s="14"/>
+      <c r="G205" s="14"/>
+      <c r="H205" s="6"/>
+    </row>
+    <row r="206" ht="15" customHeight="1" spans="1:8">
+      <c r="A206" s="3">
         <v>44641</v>
       </c>
-      <c r="B206" s="4" t="n">
+      <c r="B206" s="4">
         <v>3</v>
       </c>
       <c r="C206" s="4" t="s">
@@ -3687,11 +4406,11 @@
       <c r="G206" s="4"/>
       <c r="H206" s="4"/>
     </row>
-    <row r="207" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="3" t="n">
+    <row r="207" spans="1:8">
+      <c r="A207" s="3">
         <v>44642</v>
       </c>
-      <c r="B207" s="4" t="n">
+      <c r="B207" s="4">
         <v>4</v>
       </c>
       <c r="C207" s="4" t="s">
@@ -3703,11 +4422,11 @@
       <c r="G207" s="4"/>
       <c r="H207" s="4"/>
     </row>
-    <row r="208" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="3" t="n">
+    <row r="208" spans="1:8">
+      <c r="A208" s="3">
         <v>44643</v>
       </c>
-      <c r="B208" s="4" t="n">
+      <c r="B208" s="4">
         <v>5</v>
       </c>
       <c r="C208" s="4" t="s">
@@ -3719,11 +4438,11 @@
       <c r="G208" s="4"/>
       <c r="H208" s="4"/>
     </row>
-    <row r="209" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="3" t="n">
+    <row r="209" spans="1:8">
+      <c r="A209" s="3">
         <v>44644</v>
       </c>
-      <c r="B209" s="4" t="n">
+      <c r="B209" s="4">
         <v>6</v>
       </c>
       <c r="C209" s="4" t="s">
@@ -3735,11 +4454,11 @@
       <c r="G209" s="4"/>
       <c r="H209" s="4"/>
     </row>
-    <row r="210" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="3" t="n">
+    <row r="210" spans="1:8">
+      <c r="A210" s="3">
         <v>44645</v>
       </c>
-      <c r="B210" s="4" t="n">
+      <c r="B210" s="4">
         <v>7</v>
       </c>
       <c r="C210" s="4" t="s">
@@ -3751,39 +4470,39 @@
       <c r="G210" s="4"/>
       <c r="H210" s="4"/>
     </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A211" s="3" t="n">
+    <row r="211" ht="15" customHeight="1" spans="1:8">
+      <c r="A211" s="3">
         <v>44646</v>
       </c>
       <c r="B211" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C211" s="5"/>
-      <c r="D211" s="5"/>
-      <c r="E211" s="5"/>
-      <c r="F211" s="5"/>
-      <c r="G211" s="5"/>
-      <c r="H211" s="5"/>
-    </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A212" s="3" t="n">
+      <c r="C211" s="14"/>
+      <c r="D211" s="14"/>
+      <c r="E211" s="14"/>
+      <c r="F211" s="14"/>
+      <c r="G211" s="14"/>
+      <c r="H211" s="6"/>
+    </row>
+    <row r="212" ht="15" customHeight="1" spans="1:8">
+      <c r="A212" s="3">
         <v>44647</v>
       </c>
       <c r="B212" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C212" s="5"/>
-      <c r="D212" s="5"/>
-      <c r="E212" s="5"/>
-      <c r="F212" s="5"/>
-      <c r="G212" s="5"/>
-      <c r="H212" s="5"/>
-    </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A213" s="3" t="n">
+      <c r="C212" s="14"/>
+      <c r="D212" s="14"/>
+      <c r="E212" s="14"/>
+      <c r="F212" s="14"/>
+      <c r="G212" s="14"/>
+      <c r="H212" s="6"/>
+    </row>
+    <row r="213" ht="15" customHeight="1" spans="1:8">
+      <c r="A213" s="3">
         <v>44648</v>
       </c>
-      <c r="B213" s="4" t="n">
+      <c r="B213" s="4">
         <v>1</v>
       </c>
       <c r="C213" s="4" t="s">
@@ -3795,11 +4514,11 @@
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
     </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A214" s="3" t="n">
+    <row r="214" ht="15" customHeight="1" spans="1:8">
+      <c r="A214" s="3">
         <v>44649</v>
       </c>
-      <c r="B214" s="4" t="n">
+      <c r="B214" s="4">
         <v>2</v>
       </c>
       <c r="C214" s="4" t="s">
@@ -3811,11 +4530,11 @@
       <c r="G214" s="4"/>
       <c r="H214" s="4"/>
     </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A215" s="3" t="n">
+    <row r="215" ht="15" customHeight="1" spans="1:8">
+      <c r="A215" s="3">
         <v>44650</v>
       </c>
-      <c r="B215" s="4" t="n">
+      <c r="B215" s="4">
         <v>3</v>
       </c>
       <c r="C215" s="4" t="s">
@@ -3827,11 +4546,11 @@
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
     </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A216" s="3" t="n">
+    <row r="216" ht="15" customHeight="1" spans="1:8">
+      <c r="A216" s="3">
         <v>44651</v>
       </c>
-      <c r="B216" s="4" t="n">
+      <c r="B216" s="4">
         <v>4</v>
       </c>
       <c r="C216" s="4" t="s">
@@ -3843,151 +4562,151 @@
       <c r="G216" s="4"/>
       <c r="H216" s="4"/>
     </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A217" s="3" t="n">
+    <row r="217" ht="15" customHeight="1" spans="1:8">
+      <c r="A217" s="3">
         <v>44652</v>
       </c>
-      <c r="B217" s="9" t="s">
+      <c r="B217" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C217" s="9"/>
-      <c r="D217" s="9"/>
-      <c r="E217" s="9"/>
-      <c r="F217" s="9"/>
-      <c r="G217" s="9"/>
-      <c r="H217" s="9"/>
-    </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A218" s="3" t="n">
+      <c r="C217" s="16"/>
+      <c r="D217" s="16"/>
+      <c r="E217" s="16"/>
+      <c r="F217" s="16"/>
+      <c r="G217" s="16"/>
+      <c r="H217" s="17"/>
+    </row>
+    <row r="218" ht="15" customHeight="1" spans="1:8">
+      <c r="A218" s="3">
         <v>44653</v>
       </c>
-      <c r="B218" s="9" t="s">
+      <c r="B218" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C218" s="9"/>
-      <c r="D218" s="9"/>
-      <c r="E218" s="9"/>
-      <c r="F218" s="9"/>
-      <c r="G218" s="9"/>
-      <c r="H218" s="9"/>
-    </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A219" s="3" t="n">
+      <c r="C218" s="16"/>
+      <c r="D218" s="16"/>
+      <c r="E218" s="16"/>
+      <c r="F218" s="16"/>
+      <c r="G218" s="16"/>
+      <c r="H218" s="17"/>
+    </row>
+    <row r="219" ht="15" customHeight="1" spans="1:8">
+      <c r="A219" s="3">
         <v>44654</v>
       </c>
-      <c r="B219" s="9" t="s">
+      <c r="B219" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C219" s="9"/>
-      <c r="D219" s="9"/>
-      <c r="E219" s="9"/>
-      <c r="F219" s="9"/>
-      <c r="G219" s="9"/>
-      <c r="H219" s="9"/>
-    </row>
-    <row r="220" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A220" s="3" t="n">
+      <c r="C219" s="16"/>
+      <c r="D219" s="16"/>
+      <c r="E219" s="16"/>
+      <c r="F219" s="16"/>
+      <c r="G219" s="16"/>
+      <c r="H219" s="17"/>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220" s="3">
         <v>44655</v>
       </c>
-      <c r="B220" s="9" t="s">
+      <c r="B220" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C220" s="9"/>
-      <c r="D220" s="9"/>
-      <c r="E220" s="9"/>
-      <c r="F220" s="9"/>
-      <c r="G220" s="9"/>
-      <c r="H220" s="9"/>
-    </row>
-    <row r="221" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A221" s="3" t="n">
+      <c r="C220" s="16"/>
+      <c r="D220" s="16"/>
+      <c r="E220" s="16"/>
+      <c r="F220" s="16"/>
+      <c r="G220" s="16"/>
+      <c r="H220" s="17"/>
+    </row>
+    <row r="221" spans="1:8">
+      <c r="A221" s="3">
         <v>44656</v>
       </c>
-      <c r="B221" s="9" t="s">
+      <c r="B221" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C221" s="9"/>
-      <c r="D221" s="9"/>
-      <c r="E221" s="9"/>
-      <c r="F221" s="9"/>
-      <c r="G221" s="9"/>
-      <c r="H221" s="9"/>
-    </row>
-    <row r="222" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A222" s="3" t="n">
+      <c r="C221" s="16"/>
+      <c r="D221" s="16"/>
+      <c r="E221" s="16"/>
+      <c r="F221" s="16"/>
+      <c r="G221" s="16"/>
+      <c r="H221" s="17"/>
+    </row>
+    <row r="222" spans="1:8">
+      <c r="A222" s="3">
         <v>44657</v>
       </c>
-      <c r="B222" s="9" t="s">
+      <c r="B222" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C222" s="9"/>
-      <c r="D222" s="9"/>
-      <c r="E222" s="9"/>
-      <c r="F222" s="9"/>
-      <c r="G222" s="9"/>
-      <c r="H222" s="9"/>
-    </row>
-    <row r="223" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A223" s="3" t="n">
+      <c r="C222" s="16"/>
+      <c r="D222" s="16"/>
+      <c r="E222" s="16"/>
+      <c r="F222" s="16"/>
+      <c r="G222" s="16"/>
+      <c r="H222" s="17"/>
+    </row>
+    <row r="223" spans="1:8">
+      <c r="A223" s="3">
         <v>44658</v>
       </c>
-      <c r="B223" s="9" t="s">
+      <c r="B223" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C223" s="9"/>
-      <c r="D223" s="9"/>
-      <c r="E223" s="9"/>
-      <c r="F223" s="9"/>
-      <c r="G223" s="9"/>
-      <c r="H223" s="9"/>
-    </row>
-    <row r="224" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A224" s="3" t="n">
+      <c r="C223" s="16"/>
+      <c r="D223" s="16"/>
+      <c r="E223" s="16"/>
+      <c r="F223" s="16"/>
+      <c r="G223" s="16"/>
+      <c r="H223" s="17"/>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224" s="3">
         <v>44659</v>
       </c>
-      <c r="B224" s="9" t="s">
+      <c r="B224" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C224" s="9"/>
-      <c r="D224" s="9"/>
-      <c r="E224" s="9"/>
-      <c r="F224" s="9"/>
-      <c r="G224" s="9"/>
-      <c r="H224" s="9"/>
-    </row>
-    <row r="225" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A225" s="3" t="n">
+      <c r="C224" s="16"/>
+      <c r="D224" s="16"/>
+      <c r="E224" s="16"/>
+      <c r="F224" s="16"/>
+      <c r="G224" s="16"/>
+      <c r="H224" s="17"/>
+    </row>
+    <row r="225" spans="1:8">
+      <c r="A225" s="3">
         <v>44660</v>
       </c>
-      <c r="B225" s="9" t="s">
+      <c r="B225" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C225" s="9"/>
-      <c r="D225" s="9"/>
-      <c r="E225" s="9"/>
-      <c r="F225" s="9"/>
-      <c r="G225" s="9"/>
-      <c r="H225" s="9"/>
-    </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A226" s="3" t="n">
+      <c r="C225" s="16"/>
+      <c r="D225" s="16"/>
+      <c r="E225" s="16"/>
+      <c r="F225" s="16"/>
+      <c r="G225" s="16"/>
+      <c r="H225" s="17"/>
+    </row>
+    <row r="226" ht="15" customHeight="1" spans="1:8">
+      <c r="A226" s="3">
         <v>44661</v>
       </c>
-      <c r="B226" s="9" t="s">
+      <c r="B226" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C226" s="9"/>
-      <c r="D226" s="9"/>
-      <c r="E226" s="9"/>
-      <c r="F226" s="9"/>
-      <c r="G226" s="9"/>
-      <c r="H226" s="9"/>
-    </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A227" s="3" t="n">
+      <c r="C226" s="16"/>
+      <c r="D226" s="16"/>
+      <c r="E226" s="16"/>
+      <c r="F226" s="16"/>
+      <c r="G226" s="16"/>
+      <c r="H226" s="17"/>
+    </row>
+    <row r="227" ht="15" customHeight="1" spans="1:8">
+      <c r="A227" s="3">
         <v>44662</v>
       </c>
-      <c r="B227" s="4" t="n">
+      <c r="B227" s="4">
         <v>5</v>
       </c>
       <c r="C227" s="4" t="s">
@@ -3999,11 +4718,11 @@
       <c r="G227" s="4"/>
       <c r="H227" s="4"/>
     </row>
-    <row r="228" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="3" t="n">
+    <row r="228" spans="1:8">
+      <c r="A228" s="3">
         <v>44663</v>
       </c>
-      <c r="B228" s="4" t="n">
+      <c r="B228" s="4">
         <v>6</v>
       </c>
       <c r="C228" s="4" t="s">
@@ -4015,11 +4734,11 @@
       <c r="G228" s="4"/>
       <c r="H228" s="4"/>
     </row>
-    <row r="229" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="3" t="n">
+    <row r="229" spans="1:8">
+      <c r="A229" s="3">
         <v>44664</v>
       </c>
-      <c r="B229" s="4" t="n">
+      <c r="B229" s="4">
         <v>7</v>
       </c>
       <c r="C229" s="4" t="s">
@@ -4031,11 +4750,11 @@
       <c r="G229" s="4"/>
       <c r="H229" s="4"/>
     </row>
-    <row r="230" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="3" t="n">
+    <row r="230" spans="1:8">
+      <c r="A230" s="3">
         <v>44665</v>
       </c>
-      <c r="B230" s="4" t="n">
+      <c r="B230" s="4">
         <v>1</v>
       </c>
       <c r="C230" s="4" t="s">
@@ -4047,11 +4766,11 @@
       <c r="G230" s="4"/>
       <c r="H230" s="4"/>
     </row>
-    <row r="231" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="3" t="n">
+    <row r="231" spans="1:8">
+      <c r="A231" s="3">
         <v>44666</v>
       </c>
-      <c r="B231" s="4" t="n">
+      <c r="B231" s="4">
         <v>2</v>
       </c>
       <c r="C231" s="4" t="s">
@@ -4063,39 +4782,39 @@
       <c r="G231" s="4"/>
       <c r="H231" s="4"/>
     </row>
-    <row r="232" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A232" s="3" t="n">
+    <row r="232" spans="1:8">
+      <c r="A232" s="3">
         <v>44667</v>
       </c>
       <c r="B232" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C232" s="5"/>
-      <c r="D232" s="5"/>
-      <c r="E232" s="5"/>
-      <c r="F232" s="5"/>
-      <c r="G232" s="5"/>
-      <c r="H232" s="5"/>
-    </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A233" s="3" t="n">
+      <c r="C232" s="14"/>
+      <c r="D232" s="14"/>
+      <c r="E232" s="14"/>
+      <c r="F232" s="14"/>
+      <c r="G232" s="14"/>
+      <c r="H232" s="6"/>
+    </row>
+    <row r="233" ht="15" customHeight="1" spans="1:8">
+      <c r="A233" s="3">
         <v>44668</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C233" s="5"/>
-      <c r="D233" s="5"/>
-      <c r="E233" s="5"/>
-      <c r="F233" s="5"/>
-      <c r="G233" s="5"/>
-      <c r="H233" s="5"/>
-    </row>
-    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A234" s="3" t="n">
+      <c r="C233" s="14"/>
+      <c r="D233" s="14"/>
+      <c r="E233" s="14"/>
+      <c r="F233" s="14"/>
+      <c r="G233" s="14"/>
+      <c r="H233" s="6"/>
+    </row>
+    <row r="234" ht="15" customHeight="1" spans="1:8">
+      <c r="A234" s="3">
         <v>44669</v>
       </c>
-      <c r="B234" s="4" t="n">
+      <c r="B234" s="4">
         <v>3</v>
       </c>
       <c r="C234" s="4" t="s">
@@ -4107,11 +4826,11 @@
       <c r="G234" s="4"/>
       <c r="H234" s="4"/>
     </row>
-    <row r="235" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="3" t="n">
+    <row r="235" spans="1:8">
+      <c r="A235" s="3">
         <v>44670</v>
       </c>
-      <c r="B235" s="4" t="n">
+      <c r="B235" s="4">
         <v>4</v>
       </c>
       <c r="C235" s="4" t="s">
@@ -4123,11 +4842,11 @@
       <c r="G235" s="4"/>
       <c r="H235" s="4"/>
     </row>
-    <row r="236" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="3" t="n">
+    <row r="236" spans="1:8">
+      <c r="A236" s="3">
         <v>44671</v>
       </c>
-      <c r="B236" s="4" t="n">
+      <c r="B236" s="4">
         <v>5</v>
       </c>
       <c r="C236" s="4" t="s">
@@ -4139,11 +4858,11 @@
       <c r="G236" s="4"/>
       <c r="H236" s="4"/>
     </row>
-    <row r="237" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="3" t="n">
+    <row r="237" spans="1:8">
+      <c r="A237" s="3">
         <v>44672</v>
       </c>
-      <c r="B237" s="4" t="n">
+      <c r="B237" s="4">
         <v>6</v>
       </c>
       <c r="C237" s="4" t="s">
@@ -4155,11 +4874,11 @@
       <c r="G237" s="4"/>
       <c r="H237" s="4"/>
     </row>
-    <row r="238" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="3" t="n">
+    <row r="238" spans="1:8">
+      <c r="A238" s="3">
         <v>44673</v>
       </c>
-      <c r="B238" s="4" t="n">
+      <c r="B238" s="4">
         <v>7</v>
       </c>
       <c r="C238" s="4" t="s">
@@ -4171,39 +4890,39 @@
       <c r="G238" s="4"/>
       <c r="H238" s="4"/>
     </row>
-    <row r="239" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A239" s="3" t="n">
+    <row r="239" spans="1:8">
+      <c r="A239" s="3">
         <v>44674</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C239" s="5"/>
-      <c r="D239" s="5"/>
-      <c r="E239" s="5"/>
-      <c r="F239" s="5"/>
-      <c r="G239" s="5"/>
-      <c r="H239" s="5"/>
-    </row>
-    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A240" s="3" t="n">
+      <c r="C239" s="14"/>
+      <c r="D239" s="14"/>
+      <c r="E239" s="14"/>
+      <c r="F239" s="14"/>
+      <c r="G239" s="14"/>
+      <c r="H239" s="6"/>
+    </row>
+    <row r="240" ht="15" customHeight="1" spans="1:8">
+      <c r="A240" s="3">
         <v>44675</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C240" s="5"/>
-      <c r="D240" s="5"/>
-      <c r="E240" s="5"/>
-      <c r="F240" s="5"/>
-      <c r="G240" s="5"/>
-      <c r="H240" s="5"/>
-    </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A241" s="3" t="n">
+      <c r="C240" s="14"/>
+      <c r="D240" s="14"/>
+      <c r="E240" s="14"/>
+      <c r="F240" s="14"/>
+      <c r="G240" s="14"/>
+      <c r="H240" s="6"/>
+    </row>
+    <row r="241" ht="15" customHeight="1" spans="1:8">
+      <c r="A241" s="3">
         <v>44676</v>
       </c>
-      <c r="B241" s="4" t="n">
+      <c r="B241" s="4">
         <v>1</v>
       </c>
       <c r="C241" s="4" t="s">
@@ -4215,11 +4934,11 @@
       <c r="G241" s="4"/>
       <c r="H241" s="4"/>
     </row>
-    <row r="242" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="3" t="n">
+    <row r="242" spans="1:8">
+      <c r="A242" s="3">
         <v>44677</v>
       </c>
-      <c r="B242" s="4" t="n">
+      <c r="B242" s="4">
         <v>2</v>
       </c>
       <c r="C242" s="4" t="s">
@@ -4231,11 +4950,11 @@
       <c r="G242" s="4"/>
       <c r="H242" s="4"/>
     </row>
-    <row r="243" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="3" t="n">
+    <row r="243" spans="1:8">
+      <c r="A243" s="3">
         <v>44678</v>
       </c>
-      <c r="B243" s="4" t="n">
+      <c r="B243" s="4">
         <v>3</v>
       </c>
       <c r="C243" s="4" t="s">
@@ -4247,11 +4966,11 @@
       <c r="G243" s="4"/>
       <c r="H243" s="4"/>
     </row>
-    <row r="244" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="3" t="n">
+    <row r="244" spans="1:8">
+      <c r="A244" s="3">
         <v>44679</v>
       </c>
-      <c r="B244" s="4" t="n">
+      <c r="B244" s="4">
         <v>4</v>
       </c>
       <c r="C244" s="4" t="s">
@@ -4263,11 +4982,11 @@
       <c r="G244" s="4"/>
       <c r="H244" s="4"/>
     </row>
-    <row r="245" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="3" t="n">
+    <row r="245" spans="1:8">
+      <c r="A245" s="3">
         <v>44680</v>
       </c>
-      <c r="B245" s="4" t="n">
+      <c r="B245" s="4">
         <v>5</v>
       </c>
       <c r="C245" s="4" t="s">
@@ -4279,39 +4998,39 @@
       <c r="G245" s="4"/>
       <c r="H245" s="4"/>
     </row>
-    <row r="246" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A246" s="3" t="n">
+    <row r="246" spans="1:8">
+      <c r="A246" s="3">
         <v>44681</v>
       </c>
       <c r="B246" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C246" s="5"/>
-      <c r="D246" s="5"/>
-      <c r="E246" s="5"/>
-      <c r="F246" s="5"/>
-      <c r="G246" s="5"/>
-      <c r="H246" s="5"/>
-    </row>
-    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A247" s="3" t="n">
+      <c r="C246" s="14"/>
+      <c r="D246" s="14"/>
+      <c r="E246" s="14"/>
+      <c r="F246" s="14"/>
+      <c r="G246" s="14"/>
+      <c r="H246" s="6"/>
+    </row>
+    <row r="247" ht="15" customHeight="1" spans="1:8">
+      <c r="A247" s="3">
         <v>44682</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C247" s="5"/>
-      <c r="D247" s="5"/>
-      <c r="E247" s="5"/>
-      <c r="F247" s="5"/>
-      <c r="G247" s="5"/>
-      <c r="H247" s="5"/>
-    </row>
-    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A248" s="3" t="n">
+      <c r="C247" s="14"/>
+      <c r="D247" s="14"/>
+      <c r="E247" s="14"/>
+      <c r="F247" s="14"/>
+      <c r="G247" s="14"/>
+      <c r="H247" s="6"/>
+    </row>
+    <row r="248" ht="15" customHeight="1" spans="1:8">
+      <c r="A248" s="3">
         <v>44683</v>
       </c>
-      <c r="B248" s="4" t="n">
+      <c r="B248" s="4">
         <v>6</v>
       </c>
       <c r="C248" s="4" t="s">
@@ -4323,11 +5042,11 @@
       <c r="G248" s="4"/>
       <c r="H248" s="4"/>
     </row>
-    <row r="249" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="3" t="n">
+    <row r="249" spans="1:8">
+      <c r="A249" s="3">
         <v>44684</v>
       </c>
-      <c r="B249" s="4" t="n">
+      <c r="B249" s="4">
         <v>7</v>
       </c>
       <c r="C249" s="4" t="s">
@@ -4339,11 +5058,11 @@
       <c r="G249" s="4"/>
       <c r="H249" s="4"/>
     </row>
-    <row r="250" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="3" t="n">
+    <row r="250" spans="1:8">
+      <c r="A250" s="3">
         <v>44685</v>
       </c>
-      <c r="B250" s="4" t="n">
+      <c r="B250" s="4">
         <v>1</v>
       </c>
       <c r="C250" s="4" t="s">
@@ -4355,11 +5074,11 @@
       <c r="G250" s="4"/>
       <c r="H250" s="4"/>
     </row>
-    <row r="251" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="3" t="n">
+    <row r="251" spans="1:8">
+      <c r="A251" s="3">
         <v>44686</v>
       </c>
-      <c r="B251" s="4" t="n">
+      <c r="B251" s="4">
         <v>2</v>
       </c>
       <c r="C251" s="4" t="s">
@@ -4371,11 +5090,11 @@
       <c r="G251" s="4"/>
       <c r="H251" s="4"/>
     </row>
-    <row r="252" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="3" t="n">
+    <row r="252" spans="1:8">
+      <c r="A252" s="3">
         <v>44687</v>
       </c>
-      <c r="B252" s="4" t="n">
+      <c r="B252" s="4">
         <v>3</v>
       </c>
       <c r="C252" s="4" t="s">
@@ -4387,39 +5106,39 @@
       <c r="G252" s="4"/>
       <c r="H252" s="4"/>
     </row>
-    <row r="253" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A253" s="3" t="n">
+    <row r="253" spans="1:8">
+      <c r="A253" s="3">
         <v>44688</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C253" s="5"/>
-      <c r="D253" s="5"/>
-      <c r="E253" s="5"/>
-      <c r="F253" s="5"/>
-      <c r="G253" s="5"/>
-      <c r="H253" s="5"/>
-    </row>
-    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A254" s="3" t="n">
+      <c r="C253" s="14"/>
+      <c r="D253" s="14"/>
+      <c r="E253" s="14"/>
+      <c r="F253" s="14"/>
+      <c r="G253" s="14"/>
+      <c r="H253" s="6"/>
+    </row>
+    <row r="254" ht="15" customHeight="1" spans="1:8">
+      <c r="A254" s="3">
         <v>44689</v>
       </c>
       <c r="B254" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C254" s="5"/>
-      <c r="D254" s="5"/>
-      <c r="E254" s="5"/>
-      <c r="F254" s="5"/>
-      <c r="G254" s="5"/>
-      <c r="H254" s="5"/>
-    </row>
-    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A255" s="3" t="n">
+      <c r="C254" s="14"/>
+      <c r="D254" s="14"/>
+      <c r="E254" s="14"/>
+      <c r="F254" s="14"/>
+      <c r="G254" s="14"/>
+      <c r="H254" s="6"/>
+    </row>
+    <row r="255" ht="15" customHeight="1" spans="1:8">
+      <c r="A255" s="3">
         <v>44690</v>
       </c>
-      <c r="B255" s="4" t="n">
+      <c r="B255" s="4">
         <v>4</v>
       </c>
       <c r="C255" s="4" t="s">
@@ -4431,11 +5150,11 @@
       <c r="G255" s="4"/>
       <c r="H255" s="4"/>
     </row>
-    <row r="256" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="3" t="n">
+    <row r="256" spans="1:8">
+      <c r="A256" s="3">
         <v>44691</v>
       </c>
-      <c r="B256" s="4" t="n">
+      <c r="B256" s="4">
         <v>5</v>
       </c>
       <c r="C256" s="4" t="s">
@@ -4447,11 +5166,11 @@
       <c r="G256" s="4"/>
       <c r="H256" s="4"/>
     </row>
-    <row r="257" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="3" t="n">
+    <row r="257" spans="1:8">
+      <c r="A257" s="3">
         <v>44692</v>
       </c>
-      <c r="B257" s="4" t="n">
+      <c r="B257" s="4">
         <v>6</v>
       </c>
       <c r="C257" s="4" t="s">
@@ -4463,11 +5182,11 @@
       <c r="G257" s="4"/>
       <c r="H257" s="4"/>
     </row>
-    <row r="258" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="3" t="n">
+    <row r="258" spans="1:8">
+      <c r="A258" s="3">
         <v>44693</v>
       </c>
-      <c r="B258" s="4" t="n">
+      <c r="B258" s="4">
         <v>7</v>
       </c>
       <c r="C258" s="4" t="s">
@@ -4479,11 +5198,11 @@
       <c r="G258" s="4"/>
       <c r="H258" s="4"/>
     </row>
-    <row r="259" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="3" t="n">
+    <row r="259" spans="1:8">
+      <c r="A259" s="3">
         <v>44694</v>
       </c>
-      <c r="B259" s="4" t="n">
+      <c r="B259" s="4">
         <v>1</v>
       </c>
       <c r="C259" s="4" t="s">
@@ -4495,39 +5214,39 @@
       <c r="G259" s="4"/>
       <c r="H259" s="4"/>
     </row>
-    <row r="260" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A260" s="3" t="n">
+    <row r="260" spans="1:8">
+      <c r="A260" s="3">
         <v>44695</v>
       </c>
       <c r="B260" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C260" s="5"/>
-      <c r="D260" s="5"/>
-      <c r="E260" s="5"/>
-      <c r="F260" s="5"/>
-      <c r="G260" s="5"/>
-      <c r="H260" s="5"/>
-    </row>
-    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A261" s="3" t="n">
+      <c r="C260" s="14"/>
+      <c r="D260" s="14"/>
+      <c r="E260" s="14"/>
+      <c r="F260" s="14"/>
+      <c r="G260" s="14"/>
+      <c r="H260" s="6"/>
+    </row>
+    <row r="261" ht="15" customHeight="1" spans="1:8">
+      <c r="A261" s="3">
         <v>44696</v>
       </c>
       <c r="B261" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C261" s="5"/>
-      <c r="D261" s="5"/>
-      <c r="E261" s="5"/>
-      <c r="F261" s="5"/>
-      <c r="G261" s="5"/>
-      <c r="H261" s="5"/>
-    </row>
-    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A262" s="3" t="n">
+      <c r="C261" s="14"/>
+      <c r="D261" s="14"/>
+      <c r="E261" s="14"/>
+      <c r="F261" s="14"/>
+      <c r="G261" s="14"/>
+      <c r="H261" s="6"/>
+    </row>
+    <row r="262" ht="15" customHeight="1" spans="1:8">
+      <c r="A262" s="3">
         <v>44697</v>
       </c>
-      <c r="B262" s="4" t="n">
+      <c r="B262" s="4">
         <v>2</v>
       </c>
       <c r="C262" s="4" t="s">
@@ -4539,11 +5258,11 @@
       <c r="G262" s="4"/>
       <c r="H262" s="4"/>
     </row>
-    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A263" s="3" t="n">
+    <row r="263" ht="15" customHeight="1" spans="1:8">
+      <c r="A263" s="3">
         <v>44698</v>
       </c>
-      <c r="B263" s="4" t="n">
+      <c r="B263" s="4">
         <v>3</v>
       </c>
       <c r="C263" s="4" t="s">
@@ -4555,11 +5274,11 @@
       <c r="G263" s="4"/>
       <c r="H263" s="4"/>
     </row>
-    <row r="264" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="3" t="n">
+    <row r="264" spans="1:8">
+      <c r="A264" s="3">
         <v>44699</v>
       </c>
-      <c r="B264" s="4" t="n">
+      <c r="B264" s="4">
         <v>4</v>
       </c>
       <c r="C264" s="4" t="s">
@@ -4571,11 +5290,11 @@
       <c r="G264" s="4"/>
       <c r="H264" s="4"/>
     </row>
-    <row r="265" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="3" t="n">
+    <row r="265" spans="1:8">
+      <c r="A265" s="3">
         <v>44700</v>
       </c>
-      <c r="B265" s="4" t="n">
+      <c r="B265" s="4">
         <v>5</v>
       </c>
       <c r="C265" s="4" t="s">
@@ -4587,11 +5306,11 @@
       <c r="G265" s="4"/>
       <c r="H265" s="4"/>
     </row>
-    <row r="266" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="3" t="n">
+    <row r="266" spans="1:8">
+      <c r="A266" s="3">
         <v>44701</v>
       </c>
-      <c r="B266" s="4" t="n">
+      <c r="B266" s="4">
         <v>6</v>
       </c>
       <c r="C266" s="4" t="s">
@@ -4603,53 +5322,53 @@
       <c r="G266" s="4"/>
       <c r="H266" s="4"/>
     </row>
-    <row r="267" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A267" s="3" t="n">
+    <row r="267" spans="1:8">
+      <c r="A267" s="3">
         <v>44702</v>
       </c>
       <c r="B267" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C267" s="5"/>
-      <c r="D267" s="5"/>
-      <c r="E267" s="5"/>
-      <c r="F267" s="5"/>
-      <c r="G267" s="5"/>
-      <c r="H267" s="5"/>
-    </row>
-    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A268" s="3" t="n">
+      <c r="C267" s="14"/>
+      <c r="D267" s="14"/>
+      <c r="E267" s="14"/>
+      <c r="F267" s="14"/>
+      <c r="G267" s="14"/>
+      <c r="H267" s="6"/>
+    </row>
+    <row r="268" ht="15" customHeight="1" spans="1:8">
+      <c r="A268" s="3">
         <v>44703</v>
       </c>
       <c r="B268" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C268" s="5"/>
-      <c r="D268" s="5"/>
-      <c r="E268" s="5"/>
-      <c r="F268" s="5"/>
-      <c r="G268" s="5"/>
-      <c r="H268" s="5"/>
-    </row>
-    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A269" s="3" t="n">
+      <c r="C268" s="14"/>
+      <c r="D268" s="14"/>
+      <c r="E268" s="14"/>
+      <c r="F268" s="14"/>
+      <c r="G268" s="14"/>
+      <c r="H268" s="6"/>
+    </row>
+    <row r="269" ht="15" customHeight="1" spans="1:8">
+      <c r="A269" s="3">
         <v>44704</v>
       </c>
-      <c r="B269" s="9" t="s">
+      <c r="B269" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C269" s="9"/>
-      <c r="D269" s="9"/>
-      <c r="E269" s="9"/>
-      <c r="F269" s="9"/>
-      <c r="G269" s="9"/>
-      <c r="H269" s="9"/>
-    </row>
-    <row r="270" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="3" t="n">
+      <c r="C269" s="16"/>
+      <c r="D269" s="16"/>
+      <c r="E269" s="16"/>
+      <c r="F269" s="16"/>
+      <c r="G269" s="16"/>
+      <c r="H269" s="17"/>
+    </row>
+    <row r="270" spans="1:8">
+      <c r="A270" s="3">
         <v>44705</v>
       </c>
-      <c r="B270" s="4" t="n">
+      <c r="B270" s="4">
         <v>1</v>
       </c>
       <c r="C270" s="4" t="s">
@@ -4661,11 +5380,11 @@
       <c r="G270" s="4"/>
       <c r="H270" s="4"/>
     </row>
-    <row r="271" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="3" t="n">
+    <row r="271" spans="1:8">
+      <c r="A271" s="3">
         <v>44706</v>
       </c>
-      <c r="B271" s="4" t="n">
+      <c r="B271" s="4">
         <v>2</v>
       </c>
       <c r="C271" s="4" t="s">
@@ -4677,11 +5396,11 @@
       <c r="G271" s="4"/>
       <c r="H271" s="4"/>
     </row>
-    <row r="272" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="3" t="n">
+    <row r="272" spans="1:8">
+      <c r="A272" s="3">
         <v>44707</v>
       </c>
-      <c r="B272" s="4" t="n">
+      <c r="B272" s="4">
         <v>3</v>
       </c>
       <c r="C272" s="4" t="s">
@@ -4693,11 +5412,11 @@
       <c r="G272" s="4"/>
       <c r="H272" s="4"/>
     </row>
-    <row r="273" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="3" t="n">
+    <row r="273" spans="1:8">
+      <c r="A273" s="3">
         <v>44708</v>
       </c>
-      <c r="B273" s="4" t="n">
+      <c r="B273" s="4">
         <v>4</v>
       </c>
       <c r="C273" s="4" t="s">
@@ -4709,56 +5428,56 @@
       <c r="G273" s="4"/>
       <c r="H273" s="4"/>
     </row>
-    <row r="274" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A274" s="3" t="n">
+    <row r="274" spans="1:8">
+      <c r="A274" s="3">
         <v>44709</v>
       </c>
       <c r="B274" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C274" s="5"/>
-      <c r="D274" s="5"/>
-      <c r="E274" s="5"/>
-      <c r="F274" s="5"/>
-      <c r="G274" s="5"/>
-      <c r="H274" s="5"/>
-    </row>
-    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A275" s="3" t="n">
+      <c r="C274" s="14"/>
+      <c r="D274" s="14"/>
+      <c r="E274" s="14"/>
+      <c r="F274" s="14"/>
+      <c r="G274" s="14"/>
+      <c r="H274" s="6"/>
+    </row>
+    <row r="275" ht="15" customHeight="1" spans="1:8">
+      <c r="A275" s="3">
         <v>44710</v>
       </c>
       <c r="B275" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C275" s="5"/>
-      <c r="D275" s="5"/>
-      <c r="E275" s="5"/>
-      <c r="F275" s="5"/>
-      <c r="G275" s="5"/>
-      <c r="H275" s="5"/>
-    </row>
-    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A276" s="3" t="n">
+      <c r="C275" s="14"/>
+      <c r="D275" s="14"/>
+      <c r="E275" s="14"/>
+      <c r="F275" s="14"/>
+      <c r="G275" s="14"/>
+      <c r="H275" s="6"/>
+    </row>
+    <row r="276" ht="15" customHeight="1" spans="1:8">
+      <c r="A276" s="3">
         <v>44711</v>
       </c>
       <c r="B276" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C276" s="5"/>
-      <c r="D276" s="5"/>
-      <c r="E276" s="5"/>
-      <c r="F276" s="5"/>
-      <c r="G276" s="5"/>
-      <c r="H276" s="5"/>
-    </row>
-    <row r="277" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="3" t="n">
+      <c r="C276" s="14"/>
+      <c r="D276" s="14"/>
+      <c r="E276" s="14"/>
+      <c r="F276" s="14"/>
+      <c r="G276" s="14"/>
+      <c r="H276" s="6"/>
+    </row>
+    <row r="277" spans="1:8">
+      <c r="A277" s="3">
         <v>44712</v>
       </c>
-      <c r="B277" s="4" t="n">
+      <c r="B277" s="4">
         <v>5</v>
       </c>
-      <c r="C277" s="5" t="s">
+      <c r="C277" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D277" s="4"/>
@@ -4767,14 +5486,14 @@
       <c r="G277" s="4"/>
       <c r="H277" s="4"/>
     </row>
-    <row r="278" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="3" t="n">
+    <row r="278" spans="1:8">
+      <c r="A278" s="3">
         <v>44713</v>
       </c>
-      <c r="B278" s="4" t="n">
+      <c r="B278" s="4">
         <v>6</v>
       </c>
-      <c r="C278" s="5" t="s">
+      <c r="C278" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D278" s="4"/>
@@ -4783,14 +5502,14 @@
       <c r="G278" s="4"/>
       <c r="H278" s="4"/>
     </row>
-    <row r="279" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="3" t="n">
+    <row r="279" spans="1:8">
+      <c r="A279" s="3">
         <v>44714</v>
       </c>
-      <c r="B279" s="4" t="n">
+      <c r="B279" s="4">
         <v>1</v>
       </c>
-      <c r="C279" s="5" t="s">
+      <c r="C279" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D279" s="4"/>
@@ -4799,14 +5518,14 @@
       <c r="G279" s="4"/>
       <c r="H279" s="4"/>
     </row>
-    <row r="280" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="3" t="n">
+    <row r="280" spans="1:8">
+      <c r="A280" s="3">
         <v>44715</v>
       </c>
-      <c r="B280" s="4" t="n">
+      <c r="B280" s="4">
         <v>2</v>
       </c>
-      <c r="C280" s="5" t="s">
+      <c r="C280" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D280" s="4"/>
@@ -4815,42 +5534,42 @@
       <c r="G280" s="4"/>
       <c r="H280" s="4"/>
     </row>
-    <row r="281" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A281" s="3" t="n">
+    <row r="281" spans="1:8">
+      <c r="A281" s="3">
         <v>44716</v>
       </c>
       <c r="B281" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C281" s="5"/>
-      <c r="D281" s="5"/>
-      <c r="E281" s="5"/>
-      <c r="F281" s="5"/>
-      <c r="G281" s="5"/>
-      <c r="H281" s="5"/>
-    </row>
-    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A282" s="3" t="n">
+      <c r="C281" s="14"/>
+      <c r="D281" s="14"/>
+      <c r="E281" s="14"/>
+      <c r="F281" s="14"/>
+      <c r="G281" s="14"/>
+      <c r="H281" s="6"/>
+    </row>
+    <row r="282" ht="15" customHeight="1" spans="1:8">
+      <c r="A282" s="3">
         <v>44717</v>
       </c>
       <c r="B282" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C282" s="5"/>
-      <c r="D282" s="5"/>
-      <c r="E282" s="5"/>
-      <c r="F282" s="5"/>
-      <c r="G282" s="5"/>
-      <c r="H282" s="5"/>
-    </row>
-    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A283" s="3" t="n">
+      <c r="C282" s="14"/>
+      <c r="D282" s="14"/>
+      <c r="E282" s="14"/>
+      <c r="F282" s="14"/>
+      <c r="G282" s="14"/>
+      <c r="H282" s="6"/>
+    </row>
+    <row r="283" ht="15" customHeight="1" spans="1:8">
+      <c r="A283" s="3">
         <v>44718</v>
       </c>
-      <c r="B283" s="4" t="n">
+      <c r="B283" s="4">
         <v>3</v>
       </c>
-      <c r="C283" s="5" t="s">
+      <c r="C283" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D283" s="4"/>
@@ -4859,14 +5578,14 @@
       <c r="G283" s="4"/>
       <c r="H283" s="4"/>
     </row>
-    <row r="284" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="3" t="n">
+    <row r="284" spans="1:8">
+      <c r="A284" s="3">
         <v>44719</v>
       </c>
-      <c r="B284" s="4" t="n">
+      <c r="B284" s="4">
         <v>4</v>
       </c>
-      <c r="C284" s="5" t="s">
+      <c r="C284" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D284" s="4"/>
@@ -4875,14 +5594,14 @@
       <c r="G284" s="4"/>
       <c r="H284" s="4"/>
     </row>
-    <row r="285" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="3" t="n">
+    <row r="285" spans="1:8">
+      <c r="A285" s="3">
         <v>44720</v>
       </c>
-      <c r="B285" s="4" t="n">
+      <c r="B285" s="4">
         <v>5</v>
       </c>
-      <c r="C285" s="5" t="s">
+      <c r="C285" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D285" s="4"/>
@@ -4891,14 +5610,14 @@
       <c r="G285" s="4"/>
       <c r="H285" s="4"/>
     </row>
-    <row r="286" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="3" t="n">
+    <row r="286" spans="1:8">
+      <c r="A286" s="3">
         <v>44721</v>
       </c>
-      <c r="B286" s="4" t="n">
+      <c r="B286" s="4">
         <v>6</v>
       </c>
-      <c r="C286" s="5" t="s">
+      <c r="C286" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D286" s="4"/>
@@ -4907,14 +5626,14 @@
       <c r="G286" s="4"/>
       <c r="H286" s="4"/>
     </row>
-    <row r="287" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="3" t="n">
+    <row r="287" spans="1:8">
+      <c r="A287" s="3">
         <v>44722</v>
       </c>
-      <c r="B287" s="4" t="n">
+      <c r="B287" s="4">
         <v>1</v>
       </c>
-      <c r="C287" s="5" t="s">
+      <c r="C287" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D287" s="4"/>
@@ -4923,42 +5642,42 @@
       <c r="G287" s="4"/>
       <c r="H287" s="4"/>
     </row>
-    <row r="288" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A288" s="3" t="n">
+    <row r="288" spans="1:8">
+      <c r="A288" s="3">
         <v>44723</v>
       </c>
       <c r="B288" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C288" s="5"/>
-      <c r="D288" s="5"/>
-      <c r="E288" s="5"/>
-      <c r="F288" s="5"/>
-      <c r="G288" s="5"/>
-      <c r="H288" s="5"/>
-    </row>
-    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A289" s="3" t="n">
+      <c r="C288" s="14"/>
+      <c r="D288" s="14"/>
+      <c r="E288" s="14"/>
+      <c r="F288" s="14"/>
+      <c r="G288" s="14"/>
+      <c r="H288" s="6"/>
+    </row>
+    <row r="289" ht="15" customHeight="1" spans="1:8">
+      <c r="A289" s="3">
         <v>44724</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C289" s="5"/>
-      <c r="D289" s="5"/>
-      <c r="E289" s="5"/>
-      <c r="F289" s="5"/>
-      <c r="G289" s="5"/>
-      <c r="H289" s="5"/>
-    </row>
-    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A290" s="3" t="n">
+      <c r="C289" s="14"/>
+      <c r="D289" s="14"/>
+      <c r="E289" s="14"/>
+      <c r="F289" s="14"/>
+      <c r="G289" s="14"/>
+      <c r="H289" s="6"/>
+    </row>
+    <row r="290" ht="15" customHeight="1" spans="1:8">
+      <c r="A290" s="3">
         <v>44725</v>
       </c>
-      <c r="B290" s="4" t="n">
+      <c r="B290" s="4">
         <v>2</v>
       </c>
-      <c r="C290" s="5" t="s">
+      <c r="C290" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D290" s="4"/>
@@ -4967,14 +5686,14 @@
       <c r="G290" s="4"/>
       <c r="H290" s="4"/>
     </row>
-    <row r="291" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="3" t="n">
+    <row r="291" spans="1:8">
+      <c r="A291" s="3">
         <v>44726</v>
       </c>
-      <c r="B291" s="4" t="n">
+      <c r="B291" s="4">
         <v>3</v>
       </c>
-      <c r="C291" s="5" t="s">
+      <c r="C291" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D291" s="4"/>
@@ -4983,14 +5702,14 @@
       <c r="G291" s="4"/>
       <c r="H291" s="4"/>
     </row>
-    <row r="292" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="3" t="n">
+    <row r="292" spans="1:8">
+      <c r="A292" s="3">
         <v>44727</v>
       </c>
-      <c r="B292" s="4" t="n">
+      <c r="B292" s="4">
         <v>4</v>
       </c>
-      <c r="C292" s="5" t="s">
+      <c r="C292" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D292" s="4"/>
@@ -4999,14 +5718,14 @@
       <c r="G292" s="4"/>
       <c r="H292" s="4"/>
     </row>
-    <row r="293" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="3" t="n">
+    <row r="293" spans="1:8">
+      <c r="A293" s="3">
         <v>44728</v>
       </c>
-      <c r="B293" s="4" t="n">
+      <c r="B293" s="4">
         <v>5</v>
       </c>
-      <c r="C293" s="5" t="s">
+      <c r="C293" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D293" s="4"/>
@@ -5015,14 +5734,14 @@
       <c r="G293" s="4"/>
       <c r="H293" s="4"/>
     </row>
-    <row r="294" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="3" t="n">
+    <row r="294" spans="1:8">
+      <c r="A294" s="3">
         <v>44729</v>
       </c>
-      <c r="B294" s="4" t="n">
+      <c r="B294" s="4">
         <v>6</v>
       </c>
-      <c r="C294" s="5" t="s">
+      <c r="C294" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D294" s="4"/>
@@ -5031,42 +5750,42 @@
       <c r="G294" s="4"/>
       <c r="H294" s="4"/>
     </row>
-    <row r="295" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A295" s="3" t="n">
+    <row r="295" spans="1:8">
+      <c r="A295" s="3">
         <v>44730</v>
       </c>
       <c r="B295" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C295" s="5"/>
-      <c r="D295" s="5"/>
-      <c r="E295" s="5"/>
-      <c r="F295" s="5"/>
-      <c r="G295" s="5"/>
-      <c r="H295" s="5"/>
-    </row>
-    <row r="296" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A296" s="3" t="n">
+      <c r="C295" s="14"/>
+      <c r="D295" s="14"/>
+      <c r="E295" s="14"/>
+      <c r="F295" s="14"/>
+      <c r="G295" s="14"/>
+      <c r="H295" s="6"/>
+    </row>
+    <row r="296" spans="1:8">
+      <c r="A296" s="3">
         <v>44731</v>
       </c>
       <c r="B296" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C296" s="5"/>
-      <c r="D296" s="5"/>
-      <c r="E296" s="5"/>
-      <c r="F296" s="5"/>
-      <c r="G296" s="5"/>
-      <c r="H296" s="5"/>
-    </row>
-    <row r="297" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="3" t="n">
+      <c r="C296" s="14"/>
+      <c r="D296" s="14"/>
+      <c r="E296" s="14"/>
+      <c r="F296" s="14"/>
+      <c r="G296" s="14"/>
+      <c r="H296" s="6"/>
+    </row>
+    <row r="297" spans="1:8">
+      <c r="A297" s="3">
         <v>44732</v>
       </c>
-      <c r="B297" s="4" t="n">
+      <c r="B297" s="4">
         <v>1</v>
       </c>
-      <c r="C297" s="5" t="s">
+      <c r="C297" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D297" s="4"/>
@@ -5075,14 +5794,14 @@
       <c r="G297" s="4"/>
       <c r="H297" s="4"/>
     </row>
-    <row r="298" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="3" t="n">
+    <row r="298" spans="1:8">
+      <c r="A298" s="3">
         <v>44733</v>
       </c>
-      <c r="B298" s="4" t="n">
+      <c r="B298" s="4">
         <v>2</v>
       </c>
-      <c r="C298" s="5" t="s">
+      <c r="C298" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D298" s="4"/>
@@ -5091,14 +5810,14 @@
       <c r="G298" s="4"/>
       <c r="H298" s="4"/>
     </row>
-    <row r="299" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="3" t="n">
+    <row r="299" spans="1:8">
+      <c r="A299" s="3">
         <v>44734</v>
       </c>
-      <c r="B299" s="4" t="n">
+      <c r="B299" s="4">
         <v>3</v>
       </c>
-      <c r="C299" s="5" t="s">
+      <c r="C299" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D299" s="4"/>
@@ -5107,14 +5826,14 @@
       <c r="G299" s="4"/>
       <c r="H299" s="4"/>
     </row>
-    <row r="300" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="3" t="n">
+    <row r="300" spans="1:8">
+      <c r="A300" s="3">
         <v>44735</v>
       </c>
-      <c r="B300" s="4" t="n">
+      <c r="B300" s="4">
         <v>4</v>
       </c>
-      <c r="C300" s="5" t="s">
+      <c r="C300" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D300" s="4"/>
@@ -5123,19 +5842,19 @@
       <c r="G300" s="4"/>
       <c r="H300" s="4"/>
     </row>
-    <row r="301" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A301" s="3" t="n">
+    <row r="301" spans="1:8">
+      <c r="A301" s="3">
         <v>44736</v>
       </c>
-      <c r="B301" s="9" t="s">
+      <c r="B301" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C301" s="9"/>
-      <c r="D301" s="9"/>
-      <c r="E301" s="9"/>
-      <c r="F301" s="9"/>
-      <c r="G301" s="9"/>
-      <c r="H301" s="9"/>
+      <c r="C301" s="12"/>
+      <c r="D301" s="12"/>
+      <c r="E301" s="12"/>
+      <c r="F301" s="12"/>
+      <c r="G301" s="12"/>
+      <c r="H301" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="103">
@@ -5243,212 +5962,208 @@
     <mergeCell ref="B296:H296"/>
     <mergeCell ref="B301:H301"/>
   </mergeCells>
+  <conditionalFormatting sqref="B5:H5">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>#REF!=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A11:H11">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$A11=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>$A12=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:H5">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>#ref!=TODAY()</formula>
+  <conditionalFormatting sqref="D35:H35">
+    <cfRule type="expression" dxfId="0" priority="13">
+      <formula>$A35=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:H4 A5:A10 B6:G6 B7:H10">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>#ref!=TODAY()</formula>
+  <conditionalFormatting sqref="D42:H42">
+    <cfRule type="expression" dxfId="0" priority="10">
+      <formula>$A42=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D48:G48 D49:H49">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A48=TODAY()</formula>
+  <conditionalFormatting sqref="D46:H46">
+    <cfRule type="expression" dxfId="0" priority="9">
+      <formula>$A46=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:H47">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>$A47=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D46:H46">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A46=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D42:H42">
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A42=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D40:H41">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A40=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D38:G38 D39:H39">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A38=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D35:H35">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A35=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D33:H34">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A33=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D26:H26 D27:G27 D28:H28">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A26=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C297:C300">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A297=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C290:C294">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A290=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C283:C287">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A283=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C277:C280">
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A277=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C75">
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A75=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B300 D300:H300">
-    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A286=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B297:B299 D297:H299">
-    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A284=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B292:B294 D292:H294">
-    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A291=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B290:B291 D290:H291">
-    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A290=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B287 D287:H287">
-    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A287=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B284:B286 D284:H286">
-    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A283=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B283 D283:H283">
-    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A283=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B279:B280 D279:H280">
-    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A279=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B277:B278 D277:H278">
-    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A276=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B295:B296">
-    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A295=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B288:B289">
-    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A288=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B281:B282">
-    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A281=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B274:B276">
-    <cfRule type="expression" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A274=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B267:B268">
-    <cfRule type="expression" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A267=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B260:B261">
-    <cfRule type="expression" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A260=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B253:B254">
-    <cfRule type="expression" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A253=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B246:B247">
-    <cfRule type="expression" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A246=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B239:B240">
-    <cfRule type="expression" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A239=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B211:B212">
-    <cfRule type="expression" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A211=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A13:A1048576 B13:C14 B15:H17 B18:G18 B19:H25 B26:C28 B29:H32 B33:C35 B36:H37 B38:C42 B43:H45 B46:C49 B50:H74 B77:H203 B204:B205 B206:H210 B213:H216 B217:B226 B227:H231 B232:B233 B234:H238 B241:H245 B248:H252 B255:H259 B262:H266 B269 B270:H273 B301:H301 E13:H14">
-    <cfRule type="expression" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A13=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B76:H76 B303:H1048576">
-    <cfRule type="expression" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" dxfId="0" priority="20">
       <formula>$A75=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302:H302">
-    <cfRule type="expression" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>#ref!=TODAY()</formula>
+    <cfRule type="expression" dxfId="0" priority="42">
+      <formula>#REF!=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <conditionalFormatting sqref="B211:B212">
+    <cfRule type="expression" dxfId="0" priority="39">
+      <formula>$A211=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B239:B240">
+    <cfRule type="expression" dxfId="0" priority="38">
+      <formula>$A239=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B246:B247">
+    <cfRule type="expression" dxfId="0" priority="37">
+      <formula>$A246=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B253:B254">
+    <cfRule type="expression" dxfId="0" priority="36">
+      <formula>$A253=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B260:B261">
+    <cfRule type="expression" dxfId="0" priority="35">
+      <formula>$A260=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B267:B268">
+    <cfRule type="expression" dxfId="0" priority="34">
+      <formula>$A267=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B274:B276">
+    <cfRule type="expression" dxfId="0" priority="33">
+      <formula>$A274=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B281:B282">
+    <cfRule type="expression" dxfId="0" priority="32">
+      <formula>$A281=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B288:B289">
+    <cfRule type="expression" dxfId="0" priority="31">
+      <formula>$A288=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B295:B296">
+    <cfRule type="expression" dxfId="0" priority="30">
+      <formula>$A295=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C277:C280">
+    <cfRule type="expression" dxfId="0" priority="19">
+      <formula>$A277=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C283:C287">
+    <cfRule type="expression" dxfId="0" priority="18">
+      <formula>$A283=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C290:C294">
+    <cfRule type="expression" dxfId="0" priority="17">
+      <formula>$A290=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C297:C300">
+    <cfRule type="expression" dxfId="0" priority="16">
+      <formula>$A297=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:H4 B6:G6 B7:H10 A5:A10">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>#REF!=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B206:H210 B204:B205 B213:H216 B227:H231 B217:B226 B234:H238 B232:B233 B241:H245 B269 B301:H301 B77:H203 B248:H252 B255:H259 B262:H266 B270:H273 B15:H17 B18:G18 B19:H25 B26:C28 B29:H32 B36:H37 B33:C35 B43:H45 B38:C42 B50:H74 B46:C49 B13:C14 E13:H14 A13:A1048576">
+    <cfRule type="expression" dxfId="0" priority="40">
+      <formula>$A13=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D26:H26 D27:G27 D28:H28">
+    <cfRule type="expression" dxfId="0" priority="15">
+      <formula>$A26=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D33:H34">
+    <cfRule type="expression" dxfId="0" priority="14">
+      <formula>$A33=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D38:G38 D39:H39">
+    <cfRule type="expression" dxfId="0" priority="12">
+      <formula>$A38=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D40:H41">
+    <cfRule type="expression" dxfId="0" priority="11">
+      <formula>$A40=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D48:G48 D49:H49">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>$A48=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B76:H76 B303:H1048576">
+    <cfRule type="expression" dxfId="0" priority="41">
+      <formula>$A75=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B277:B278 D277:H278">
+    <cfRule type="expression" dxfId="0" priority="29">
+      <formula>$A276=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B279:B280 D279:H280">
+    <cfRule type="expression" dxfId="0" priority="28">
+      <formula>$A279=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B283 D283:H283">
+    <cfRule type="expression" dxfId="0" priority="27">
+      <formula>$A283=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B284:B286 D284:H286">
+    <cfRule type="expression" dxfId="0" priority="26">
+      <formula>$A283=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B287 D287:H287">
+    <cfRule type="expression" dxfId="0" priority="25">
+      <formula>$A287=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B290:B291 D290:H291">
+    <cfRule type="expression" dxfId="0" priority="24">
+      <formula>$A290=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B292:B294 D292:H294">
+    <cfRule type="expression" dxfId="0" priority="23">
+      <formula>$A291=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B297:B299 D297:H299">
+    <cfRule type="expression" dxfId="0" priority="22">
+      <formula>$A284=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B300 D300:H300">
+    <cfRule type="expression" dxfId="0" priority="21">
+      <formula>$A286=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>